--- a/examsDjangoBasics.xlsx
+++ b/examsDjangoBasics.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2963" uniqueCount="1890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3116" uniqueCount="1974">
   <si>
     <t>speedApp</t>
   </si>
@@ -27118,9 +27118,6 @@
     </r>
   </si>
   <si>
-    <t>When and how self.kwargs = {'pk': 2} comes into existence in a class-based view like this one</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">    </t>
     </r>
@@ -27846,9 +27843,6 @@
     <t>URL resolver</t>
   </si>
   <si>
-    <t>Extracts {'pk': 2}</t>
-  </si>
-  <si>
     <t>View is created</t>
   </si>
   <si>
@@ -33237,13 +33231,1243 @@
   </si>
   <si>
     <t>Рендериране на формата - първо label, след това самото поле</t>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)  # test -&gt; &lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>recipes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>views</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CataloqueView</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> object at 0x000002750BE8DE10&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getattr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, attribute_name, default_value)</t>
+    </r>
+  </si>
+  <si>
+    <t>So in this example:</t>
+  </si>
+  <si>
+    <t>means:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>custom_placeholders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if it exists</t>
+    </r>
+  </si>
+  <si>
+    <t>If it doesn’t exist, use an empty dictionary {} instead."</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>custom_placeholders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> getattr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 'custom_placeholders', {})</t>
+    </r>
+  </si>
+  <si>
+    <t>Why This Is Important Here</t>
+  </si>
+  <si>
+    <t>You defined:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>When</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and how self.kwargs = {'pk': 2} comes into existence in a class-based view like this one</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>What</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getattr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  function does ?</t>
+    </r>
+  </si>
+  <si>
+    <t>Syntax:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So when </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_placeholders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">() runs on a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RecipeCreateForm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> instance:</t>
+    </r>
+  </si>
+  <si>
+    <t>self.custom_placeholders exists</t>
+  </si>
+  <si>
+    <r>
+      <t>But if another</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> form</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> used </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PlaceholderMixin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and didn’t define </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>custom_placeholders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, then:</t>
+    </r>
+  </si>
+  <si>
+    <t>self.custom_placeholders wouldn’t exist</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getattr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>() returns that dictionary</t>
+    </r>
+  </si>
+  <si>
+    <t>getattr() would return {} instead</t>
+  </si>
+  <si>
+    <t>No error would occur</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">What Would Happen Without </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getattr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>If you wrote:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>custom_placeholders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = self.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>custom_placeholders</t>
+    </r>
+  </si>
+  <si>
+    <t>Then any form that uses PlaceholderMixin but doesn’t define custom_placeholders would crash with:</t>
+  </si>
+  <si>
+    <t>AttributeError: 'SomeForm' object has no attribute 'custom_placeholders'</t>
+  </si>
+  <si>
+    <t>So getattr() makes your mixin safe and reusable.</t>
+  </si>
+  <si>
+    <t>What does this block?</t>
+  </si>
+  <si>
+    <t>Try to get a custom placeholder for that field</t>
+  </si>
+  <si>
+    <t>If not found: Use the field's label Or generate one from the field name</t>
+  </si>
+  <si>
+    <t>тук self вече има self.fields</t>
+  </si>
+  <si>
+    <t>pk=2</t>
+  </si>
+  <si>
+    <t>Extracts pk=2</t>
+  </si>
+  <si>
+    <t>Важно: Когато изберем името recipe_id това означава че в self.kwargs key-a ще ни бъде {recipe_id: some int)</t>
+  </si>
+  <si>
+    <t>Тестваме тук(в самия for loop)</t>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>field_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>label</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>title Title</t>
+  </si>
+  <si>
+    <t>print(field.widget.attrs.get('placeholder'))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title ,защото взима </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Когато принтираме на тази линия placeholde-a, получаваме вече записания placeholder Title, защото се изпълнява първо </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>field.label</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or field_name.replace('_', ' ').capitalize()</t>
+    </r>
+  </si>
+  <si>
+    <t>Django’s URL reversing system</t>
+  </si>
+  <si>
+    <t>You wrote this in your template:</t>
+  </si>
+  <si>
+    <t>And in urls.py you have:</t>
+  </si>
+  <si>
+    <t>1. The {% url %} template tag</t>
+  </si>
+  <si>
+    <t>{% url 'edit-recipe' recipe.id %} tells Django:</t>
+  </si>
+  <si>
+    <t>“Find the URL pattern named edit-recipe and fill in its dynamic parts using the argument I provide.”</t>
+  </si>
+  <si>
+    <t>2. Django finds the matching URL pattern</t>
+  </si>
+  <si>
+    <t>In your urls.py, Django sees:</t>
+  </si>
+  <si>
+    <t>path('&lt;int:recipe_id&gt;/edit/', RecipeEditView.as_view(), name='edit-recipe')</t>
+  </si>
+  <si>
+    <t>This pattern:</t>
+  </si>
+  <si>
+    <t>Has a dynamic segment: &lt;int:recipe_id&gt;</t>
+  </si>
+  <si>
+    <t>Is named: 'edit-recipe'</t>
+  </si>
+  <si>
+    <t>That &lt;int:recipe_id&gt; means:</t>
+  </si>
+  <si>
+    <t>Expect an integer</t>
+  </si>
+  <si>
+    <t>Assign it to the parameter recipe_id</t>
+  </si>
+  <si>
+    <t>3 The argument gets inserted</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ypu have in your project-level urls.py: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>path('recipe/', include('recipes.urls'))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So the pattern:  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;recipe_id&gt;/edit/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  becomes: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4/edit/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Django substitutes:  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;int:recipe_id&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If:  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>recipe.id == 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In your template:  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{% url 'edit-recipe' recipe.id %}</t>
+    </r>
+  </si>
+  <si>
+    <t>So Django combines:</t>
+  </si>
+  <si>
+    <t>recipe/        (from project urls.py)</t>
+  </si>
+  <si>
+    <t>4/edit/        (from app urls.py)</t>
+  </si>
+  <si>
+    <t>Result:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">class </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RecipeDeleteForm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ReadOnlyMixin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RecipeBaseForm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>):</t>
+    </r>
+  </si>
+  <si>
+    <t>1. custom_placeholders</t>
+  </si>
+  <si>
+    <t>Безопасен метод за достъване на клас атрибут:</t>
+  </si>
+  <si>
+    <t>2. read_only_fields</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="0.39997558519241921"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>custom_placeholders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getattr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(self, 'custom_placeholders', {})</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Тук използаме метода </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getattr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> за да достъпим клас атрибут на инстанция(self) от друг клас</t>
+    </r>
+  </si>
+  <si>
+    <t>getattr връща или стринг или празен речник</t>
+  </si>
+  <si>
+    <t>Тук използваме същото име read_only_fields = [] и му запиваме празен речник</t>
+  </si>
+  <si>
+    <t>When you access:  self.read_only_fields</t>
+  </si>
+  <si>
+    <t>Python searches in this order:</t>
+  </si>
+  <si>
+    <t>1. Instance attributes</t>
+  </si>
+  <si>
+    <t>2. Class (RecipeDeleteForm)</t>
+  </si>
+  <si>
+    <t>3. Parent class (ReadOnlyMixin)</t>
+  </si>
+  <si>
+    <t>4. Further up the inheritance chain</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read_only_fields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = []</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If it does NOT define it, Python falls back to:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read_only_fields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = []</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So:  If RecipeDeleteForm defines </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read_only_fields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, that list is used.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read_only_fields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = ['title', 'cuisine_type', 'ingredients', 'instructions', 'cooking_time', 'image_url']</t>
+    </r>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PlaceholderMixin approach:  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Used when the attribute might not exist at all.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ReadOnlyMixin approach: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>You guarantee the attribute always exists by defining it in the mixin.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>make_fields_readonly</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    def __init__(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, *args, **kwargs):</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="56" x14ac:knownFonts="1">
+  <fonts count="63" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -33684,6 +34908,57 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFDA7BB9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA47A20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFDA7BB9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -33925,7 +35200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -33975,7 +35250,6 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -34002,9 +35276,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -34014,10 +35291,10 @@
   <colors>
     <mruColors>
       <color rgb="FFA47A20"/>
+      <color rgb="FFDA7BB9"/>
+      <color rgb="FF179A77"/>
       <color rgb="FF7D7DFF"/>
       <color rgb="FFA626A4"/>
-      <color rgb="FF179A77"/>
-      <color rgb="FFDA7BB9"/>
       <color rgb="FFFF33CC"/>
     </mruColors>
   </colors>
@@ -35081,13 +36358,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>509752</xdr:colOff>
+      <xdr:colOff>540230</xdr:colOff>
       <xdr:row>1108</xdr:row>
       <xdr:rowOff>21021</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>99848</xdr:colOff>
+      <xdr:colOff>130326</xdr:colOff>
       <xdr:row>1109</xdr:row>
       <xdr:rowOff>63062</xdr:rowOff>
     </xdr:to>
@@ -35098,8 +36375,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="6605752" y="100273945"/>
-          <a:ext cx="809296" cy="225972"/>
+          <a:off x="6636230" y="202678187"/>
+          <a:ext cx="809296" cy="224921"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -35775,13 +37052,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>47297</xdr:colOff>
-      <xdr:row>1164</xdr:row>
+      <xdr:row>1217</xdr:row>
       <xdr:rowOff>42042</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>541283</xdr:colOff>
-      <xdr:row>1167</xdr:row>
+      <xdr:row>1220</xdr:row>
       <xdr:rowOff>36787</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -35822,13 +37099,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>57807</xdr:colOff>
-      <xdr:row>1225</xdr:row>
+      <xdr:row>1278</xdr:row>
       <xdr:rowOff>178676</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>273269</xdr:colOff>
-      <xdr:row>1227</xdr:row>
+      <xdr:row>1280</xdr:row>
       <xdr:rowOff>7007</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -35912,13 +37189,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>436179</xdr:colOff>
-      <xdr:row>1224</xdr:row>
+      <xdr:row>1277</xdr:row>
       <xdr:rowOff>105104</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>131379</xdr:colOff>
-      <xdr:row>1225</xdr:row>
+      <xdr:row>1278</xdr:row>
       <xdr:rowOff>52552</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -36071,6 +37348,100 @@
         </a:prstGeom>
         <a:ln>
           <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>383177</xdr:colOff>
+      <xdr:row>1145</xdr:row>
+      <xdr:rowOff>169817</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>287383</xdr:colOff>
+      <xdr:row>1148</xdr:row>
+      <xdr:rowOff>21771</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1602377" y="209593543"/>
+          <a:ext cx="4171406" cy="400594"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>8709</xdr:colOff>
+      <xdr:row>1385</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>1388</xdr:row>
+      <xdr:rowOff>17416</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Arrow Connector 14"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5495109" y="253467325"/>
+          <a:ext cx="174171" cy="413657"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -43571,7 +44942,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1283"/>
+  <dimension ref="A1:T1420"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -43685,7 +45056,7 @@
         <v>471</v>
       </c>
       <c r="H25" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -44308,7 +45679,7 @@
       <c r="B193" t="s">
         <v>1114</v>
       </c>
-      <c r="H193" s="77" t="s">
+      <c r="H193" s="75" t="s">
         <v>1104</v>
       </c>
     </row>
@@ -44342,7 +45713,7 @@
       </c>
     </row>
     <row r="198" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H198" s="77" t="s">
+      <c r="H198" s="75" t="s">
         <v>1110</v>
       </c>
     </row>
@@ -44706,114 +46077,161 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B385" t="s">
         <v>1140</v>
       </c>
     </row>
-    <row r="386" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B386" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="387" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B387" t="s">
         <v>1138</v>
       </c>
     </row>
-    <row r="388" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B388" t="s">
         <v>1146</v>
       </c>
     </row>
-    <row r="390" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B390" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="391" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B391" t="s">
         <v>1147</v>
       </c>
     </row>
-    <row r="392" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B392" t="s">
         <v>1144</v>
       </c>
     </row>
-    <row r="394" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B394" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="395" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B395" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="396" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B396" s="37" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="397" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B397" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="400" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B400" t="s">
+    <row r="400" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B400" s="26" t="s">
         <v>1253</v>
       </c>
+      <c r="C400" s="14"/>
+      <c r="D400" s="14"/>
+      <c r="E400" s="14"/>
+      <c r="F400" s="15"/>
     </row>
     <row r="401" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B401" t="s">
+      <c r="B401" s="16" t="s">
         <v>1140</v>
       </c>
+      <c r="C401" s="9"/>
+      <c r="D401" s="9"/>
+      <c r="E401" s="9"/>
+      <c r="F401" s="17"/>
     </row>
     <row r="402" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B402" t="s">
+      <c r="B402" s="16" t="s">
         <v>1252</v>
       </c>
+      <c r="C402" s="9"/>
+      <c r="D402" s="9"/>
+      <c r="E402" s="9"/>
+      <c r="F402" s="17"/>
     </row>
     <row r="403" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B403" t="s">
+      <c r="B403" s="16" t="s">
         <v>1254</v>
       </c>
+      <c r="C403" s="9"/>
+      <c r="D403" s="9"/>
+      <c r="E403" s="9"/>
+      <c r="F403" s="17"/>
       <c r="H403" t="s">
         <v>1262</v>
       </c>
     </row>
+    <row r="404" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B404" s="16"/>
+      <c r="C404" s="9"/>
+      <c r="D404" s="9"/>
+      <c r="E404" s="9"/>
+      <c r="F404" s="17"/>
+    </row>
     <row r="405" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B405" s="16"/>
+      <c r="C405" s="9"/>
+      <c r="D405" s="9"/>
+      <c r="E405" s="9"/>
+      <c r="F405" s="17"/>
       <c r="H405" t="s">
         <v>1260</v>
       </c>
     </row>
     <row r="406" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B406" t="s">
+      <c r="B406" s="16" t="s">
         <v>29</v>
       </c>
+      <c r="C406" s="9"/>
+      <c r="D406" s="9"/>
+      <c r="E406" s="9"/>
+      <c r="F406" s="17"/>
       <c r="I406" t="s">
         <v>1259</v>
       </c>
     </row>
     <row r="407" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B407" t="s">
+      <c r="B407" s="16" t="s">
         <v>1255</v>
       </c>
+      <c r="C407" s="9"/>
+      <c r="D407" s="9"/>
+      <c r="E407" s="9"/>
+      <c r="F407" s="17"/>
+      <c r="H407" t="s">
+        <v>1888</v>
+      </c>
     </row>
     <row r="408" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B408" t="s">
+      <c r="B408" s="16" t="s">
         <v>1256</v>
       </c>
+      <c r="C408" s="9"/>
+      <c r="D408" s="9"/>
+      <c r="E408" s="9"/>
+      <c r="F408" s="17"/>
       <c r="H408" t="s">
         <v>1257</v>
       </c>
     </row>
     <row r="409" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B409" t="s">
+      <c r="B409" s="18" t="s">
         <v>196</v>
       </c>
+      <c r="C409" s="19"/>
+      <c r="D409" s="19"/>
+      <c r="E409" s="19"/>
+      <c r="F409" s="20"/>
       <c r="I409" t="s">
         <v>1258</v>
       </c>
@@ -44829,7 +46247,7 @@
       </c>
       <c r="L411" s="14"/>
       <c r="M411" s="15"/>
-      <c r="N411" s="52">
+      <c r="N411" s="51">
         <v>3</v>
       </c>
     </row>
@@ -44844,7 +46262,7 @@
       </c>
       <c r="L412" s="19"/>
       <c r="M412" s="20"/>
-      <c r="N412" s="52">
+      <c r="N412" s="51">
         <v>4</v>
       </c>
     </row>
@@ -44993,7 +46411,7 @@
       <c r="H434" t="s">
         <v>1281</v>
       </c>
-      <c r="L434" s="51" t="s">
+      <c r="L434" s="50" t="s">
         <v>1278</v>
       </c>
     </row>
@@ -45008,8 +46426,8 @@
       <c r="H435" t="s">
         <v>1280</v>
       </c>
-      <c r="L435" s="62" t="s">
-        <v>1501</v>
+      <c r="L435" s="61" t="s">
+        <v>1499</v>
       </c>
     </row>
     <row r="436" spans="2:12" x14ac:dyDescent="0.3">
@@ -45145,7 +46563,7 @@
         <v>1379</v>
       </c>
       <c r="J459" s="14"/>
-      <c r="K459" s="55"/>
+      <c r="K459" s="54"/>
       <c r="L459" s="14"/>
       <c r="M459" s="14"/>
       <c r="N459" s="15"/>
@@ -45161,20 +46579,20 @@
       <c r="G460" s="22"/>
       <c r="H460" s="23"/>
       <c r="I460" s="21" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="J460" s="22"/>
-      <c r="K460" s="57"/>
+      <c r="K460" s="56"/>
       <c r="L460" s="22"/>
       <c r="M460" s="22"/>
       <c r="N460" s="23"/>
     </row>
     <row r="461" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D461" s="54">
+      <c r="D461" s="53">
         <v>2</v>
       </c>
-      <c r="E461" s="70" t="s">
-        <v>1801</v>
+      <c r="E461" s="69" t="s">
+        <v>1799</v>
       </c>
       <c r="F461" s="9"/>
       <c r="G461" s="9"/>
@@ -45183,7 +46601,7 @@
         <v>1381</v>
       </c>
       <c r="J461" s="9"/>
-      <c r="K461" s="56"/>
+      <c r="K461" s="55"/>
       <c r="L461" s="9"/>
       <c r="M461" s="9"/>
       <c r="N461" s="17"/>
@@ -45193,7 +46611,7 @@
         <v>3</v>
       </c>
       <c r="E462" s="21" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="F462" s="22"/>
       <c r="G462" s="22"/>
@@ -45202,7 +46620,7 @@
         <v>1382</v>
       </c>
       <c r="J462" s="22"/>
-      <c r="K462" s="57"/>
+      <c r="K462" s="56"/>
       <c r="L462" s="22"/>
       <c r="M462" s="22"/>
       <c r="N462" s="23"/>
@@ -45221,7 +46639,7 @@
         <v>1383</v>
       </c>
       <c r="J463" s="9"/>
-      <c r="K463" s="56"/>
+      <c r="K463" s="55"/>
       <c r="L463" s="9"/>
       <c r="M463" s="9"/>
       <c r="N463" s="17"/>
@@ -45240,7 +46658,7 @@
         <v>1384</v>
       </c>
       <c r="J464" s="22"/>
-      <c r="K464" s="57"/>
+      <c r="K464" s="56"/>
       <c r="L464" s="22"/>
       <c r="M464" s="22"/>
       <c r="N464" s="23"/>
@@ -45253,7 +46671,7 @@
       <c r="H465" s="9"/>
       <c r="I465" s="9"/>
       <c r="J465" s="9"/>
-      <c r="K465" s="56"/>
+      <c r="K465" s="55"/>
       <c r="L465" s="9"/>
       <c r="M465" s="9"/>
       <c r="N465" s="9"/>
@@ -45268,40 +46686,40 @@
       <c r="H466" s="9"/>
       <c r="I466" s="9"/>
       <c r="J466" s="9"/>
-      <c r="K466" s="56"/>
+      <c r="K466" s="55"/>
       <c r="L466" s="9"/>
       <c r="M466" s="9"/>
       <c r="N466" s="9"/>
     </row>
     <row r="467" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="E467" s="76" t="s">
-        <v>1803</v>
+      <c r="E467" s="77" t="s">
+        <v>1801</v>
       </c>
       <c r="F467" s="9"/>
       <c r="G467" s="9"/>
       <c r="H467" s="9"/>
       <c r="I467" s="9"/>
       <c r="J467" s="9"/>
-      <c r="K467" s="56"/>
+      <c r="K467" s="55"/>
       <c r="L467" s="9"/>
       <c r="M467" s="9"/>
       <c r="N467" s="9"/>
     </row>
     <row r="468" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D468" s="58"/>
+      <c r="D468" s="57"/>
       <c r="E468" s="9"/>
       <c r="F468" s="9"/>
       <c r="G468" s="9"/>
       <c r="H468" s="9"/>
       <c r="I468" s="9"/>
       <c r="J468" s="9"/>
-      <c r="K468" s="56"/>
+      <c r="K468" s="55"/>
       <c r="L468" s="9"/>
       <c r="M468" s="9"/>
       <c r="N468" s="9"/>
     </row>
     <row r="469" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D469" s="58"/>
+      <c r="D469" s="57"/>
       <c r="E469" s="9" t="s">
         <v>1387</v>
       </c>
@@ -45310,13 +46728,13 @@
       <c r="H469" s="9"/>
       <c r="I469" s="9"/>
       <c r="J469" s="9"/>
-      <c r="K469" s="56"/>
+      <c r="K469" s="55"/>
       <c r="L469" s="9"/>
       <c r="M469" s="9"/>
       <c r="N469" s="9"/>
     </row>
     <row r="470" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D470" s="58"/>
+      <c r="D470" s="57"/>
       <c r="E470" s="9" t="s">
         <v>1388</v>
       </c>
@@ -45325,13 +46743,13 @@
       <c r="H470" s="9"/>
       <c r="I470" s="9"/>
       <c r="J470" s="9"/>
-      <c r="K470" s="56"/>
+      <c r="K470" s="55"/>
       <c r="L470" s="9"/>
       <c r="M470" s="9"/>
       <c r="N470" s="9"/>
     </row>
     <row r="471" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D471" s="58"/>
+      <c r="D471" s="57"/>
       <c r="E471" s="9" t="s">
         <v>1389</v>
       </c>
@@ -45340,26 +46758,26 @@
       <c r="H471" s="9"/>
       <c r="I471" s="9"/>
       <c r="J471" s="9"/>
-      <c r="K471" s="56"/>
+      <c r="K471" s="55"/>
       <c r="L471" s="9"/>
       <c r="M471" s="9"/>
       <c r="N471" s="9"/>
     </row>
     <row r="472" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D472" s="58"/>
+      <c r="D472" s="57"/>
       <c r="F472" s="9"/>
       <c r="G472" s="9"/>
       <c r="H472" s="9"/>
       <c r="I472" s="9"/>
       <c r="J472" s="9"/>
-      <c r="K472" s="56"/>
+      <c r="K472" s="55"/>
       <c r="L472" s="9"/>
       <c r="M472" s="9"/>
       <c r="N472" s="9"/>
     </row>
     <row r="473" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D473" s="58"/>
-      <c r="E473" s="59" t="s">
+      <c r="D473" s="57"/>
+      <c r="E473" s="58" t="s">
         <v>1390</v>
       </c>
       <c r="F473" s="9"/>
@@ -45367,14 +46785,14 @@
       <c r="H473" s="9"/>
       <c r="I473" s="9"/>
       <c r="J473" s="9"/>
-      <c r="K473" s="56"/>
+      <c r="K473" s="55"/>
       <c r="L473" s="9"/>
       <c r="M473" s="9"/>
       <c r="N473" s="9"/>
     </row>
     <row r="474" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D474" s="58"/>
-      <c r="E474" s="59" t="s">
+      <c r="D474" s="57"/>
+      <c r="E474" s="58" t="s">
         <v>1391</v>
       </c>
       <c r="F474" s="9"/>
@@ -45382,13 +46800,13 @@
       <c r="H474" s="9"/>
       <c r="I474" s="9"/>
       <c r="J474" s="9"/>
-      <c r="K474" s="56"/>
+      <c r="K474" s="55"/>
       <c r="L474" s="9"/>
       <c r="M474" s="9"/>
       <c r="N474" s="9"/>
     </row>
     <row r="475" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D475" s="58"/>
+      <c r="D475" s="57"/>
       <c r="E475" s="9"/>
       <c r="F475" s="9" t="s">
         <v>1380</v>
@@ -45397,7 +46815,7 @@
       <c r="H475" s="9"/>
       <c r="I475" s="9"/>
       <c r="J475" s="9"/>
-      <c r="K475" s="56"/>
+      <c r="K475" s="55"/>
       <c r="L475" s="9"/>
       <c r="M475" s="9"/>
       <c r="N475" s="9"/>
@@ -45412,7 +46830,7 @@
       <c r="K477" s="25"/>
     </row>
     <row r="478" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="E478" s="53" t="s">
+      <c r="E478" s="52" t="s">
         <v>1408</v>
       </c>
       <c r="H478" t="s">
@@ -45421,17 +46839,17 @@
       <c r="K478" s="25"/>
     </row>
     <row r="479" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="E479" s="60" t="s">
+      <c r="E479" s="59" t="s">
         <v>1448</v>
       </c>
       <c r="K479" s="25"/>
     </row>
     <row r="480" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="E480" s="60"/>
+      <c r="E480" s="59"/>
       <c r="K480" s="25"/>
     </row>
     <row r="481" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="E481" s="61" t="s">
+      <c r="E481" s="60" t="s">
         <v>1446</v>
       </c>
       <c r="K481" s="25" t="s">
@@ -45439,7 +46857,7 @@
       </c>
     </row>
     <row r="482" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="E482" s="61" t="s">
+      <c r="E482" s="60" t="s">
         <v>1447</v>
       </c>
       <c r="K482" t="s">
@@ -45513,7 +46931,7 @@
       <c r="D496" t="s">
         <v>1402</v>
       </c>
-      <c r="K496" s="53" t="s">
+      <c r="K496" s="52" t="s">
         <v>1404</v>
       </c>
     </row>
@@ -45528,7 +46946,7 @@
     </row>
     <row r="499" spans="3:11" x14ac:dyDescent="0.3">
       <c r="E499" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="K499" s="25"/>
     </row>
@@ -45539,8 +46957,8 @@
       <c r="K500" s="25"/>
     </row>
     <row r="501" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="F501" s="71" t="s">
-        <v>1805</v>
+      <c r="F501" s="70" t="s">
+        <v>1803</v>
       </c>
       <c r="K501" s="25"/>
     </row>
@@ -45585,7 +47003,7 @@
       <c r="D508" t="s">
         <v>1299</v>
       </c>
-      <c r="K508" s="53" t="s">
+      <c r="K508" s="78" t="s">
         <v>1375</v>
       </c>
     </row>
@@ -45610,7 +47028,7 @@
         <v>1297</v>
       </c>
       <c r="K511" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="512" spans="3:11" x14ac:dyDescent="0.3">
@@ -45633,7 +47051,7 @@
       <c r="D514" t="s">
         <v>1298</v>
       </c>
-      <c r="K514" s="53" t="s">
+      <c r="K514" s="78" t="s">
         <v>1309</v>
       </c>
     </row>
@@ -45714,7 +47132,7 @@
       <c r="D536" t="s">
         <v>1315</v>
       </c>
-      <c r="L536" s="53" t="s">
+      <c r="L536" s="52" t="s">
         <v>1439</v>
       </c>
     </row>
@@ -45938,7 +47356,7 @@
       <c r="M567" s="23"/>
     </row>
     <row r="568" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D568" s="54" t="s">
+      <c r="D568" s="53" t="s">
         <v>1344</v>
       </c>
       <c r="E568" s="16" t="s">
@@ -46030,7 +47448,7 @@
       </c>
     </row>
     <row r="582" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="D582" s="53" t="s">
+      <c r="D582" s="52" t="s">
         <v>1443</v>
       </c>
       <c r="K582" t="s">
@@ -46082,122 +47500,183 @@
     </row>
     <row r="592" spans="3:11" x14ac:dyDescent="0.3">
       <c r="E592" t="s">
-        <v>1553</v>
-      </c>
-    </row>
-    <row r="593" spans="2:5" x14ac:dyDescent="0.3">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="593" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E593" t="s">
         <v>1363</v>
       </c>
     </row>
-    <row r="594" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="594" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E594" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="595" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C595" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="596" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D596" s="53" t="s">
+    <row r="596" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D596" s="52" t="s">
         <v>1365</v>
       </c>
     </row>
-    <row r="598" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="598" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D598" t="s">
         <v>1366</v>
       </c>
     </row>
-    <row r="599" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E599" t="s">
         <v>1371</v>
       </c>
     </row>
-    <row r="600" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="600" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E600" t="s">
         <v>1367</v>
       </c>
     </row>
-    <row r="601" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="601" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E601" t="s">
         <v>1368</v>
       </c>
     </row>
-    <row r="602" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E602" t="s">
         <v>1369</v>
       </c>
     </row>
-    <row r="603" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="603" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E603" t="s">
         <v>1370</v>
       </c>
     </row>
-    <row r="605" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B605" t="s">
+    <row r="605" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B605" s="26" t="s">
         <v>1416</v>
       </c>
-    </row>
-    <row r="606" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B606" t="s">
+      <c r="C605" s="14"/>
+      <c r="D605" s="14"/>
+      <c r="E605" s="14"/>
+      <c r="F605" s="15"/>
+    </row>
+    <row r="606" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B606" s="16" t="s">
         <v>1140</v>
       </c>
-    </row>
-    <row r="607" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B607" t="s">
+      <c r="C606" s="9"/>
+      <c r="D606" s="9"/>
+      <c r="E606" s="9"/>
+      <c r="F606" s="17"/>
+    </row>
+    <row r="607" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B607" s="16" t="s">
         <v>1417</v>
       </c>
-    </row>
-    <row r="608" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B608" t="s">
+      <c r="C607" s="9"/>
+      <c r="D607" s="9"/>
+      <c r="E607" s="9"/>
+      <c r="F607" s="17"/>
+    </row>
+    <row r="608" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B608" s="16" t="s">
         <v>1414</v>
       </c>
+      <c r="C608" s="9"/>
+      <c r="D608" s="9"/>
+      <c r="E608" s="9"/>
+      <c r="F608" s="17"/>
     </row>
     <row r="609" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B609" t="s">
+      <c r="B609" s="16" t="s">
         <v>1273</v>
       </c>
+      <c r="C609" s="9"/>
+      <c r="D609" s="9"/>
+      <c r="E609" s="9"/>
+      <c r="F609" s="17"/>
+      <c r="H609" s="2" t="s">
+        <v>1919</v>
+      </c>
     </row>
     <row r="610" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B610" t="s">
+      <c r="B610" s="16" t="s">
         <v>1275</v>
       </c>
+      <c r="C610" s="9"/>
+      <c r="D610" s="9"/>
+      <c r="E610" s="9"/>
+      <c r="F610" s="17"/>
     </row>
     <row r="611" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B611" t="s">
+      <c r="B611" s="16" t="s">
         <v>1415</v>
       </c>
+      <c r="C611" s="9"/>
+      <c r="D611" s="9"/>
+      <c r="E611" s="9"/>
+      <c r="F611" s="17"/>
+    </row>
+    <row r="612" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B612" s="16"/>
+      <c r="C612" s="9"/>
+      <c r="D612" s="9"/>
+      <c r="E612" s="9"/>
+      <c r="F612" s="17"/>
     </row>
     <row r="613" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B613" t="s">
+      <c r="B613" s="16" t="s">
         <v>31</v>
       </c>
+      <c r="C613" s="9"/>
+      <c r="D613" s="9"/>
+      <c r="E613" s="9"/>
+      <c r="F613" s="17"/>
     </row>
     <row r="614" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B614" t="s">
+      <c r="B614" s="16" t="s">
         <v>207</v>
       </c>
+      <c r="C614" s="9"/>
+      <c r="D614" s="9"/>
+      <c r="E614" s="9"/>
+      <c r="F614" s="17"/>
     </row>
     <row r="615" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B615" t="s">
+      <c r="B615" s="16" t="s">
         <v>1418</v>
       </c>
+      <c r="C615" s="9"/>
+      <c r="D615" s="9"/>
+      <c r="E615" s="9"/>
+      <c r="F615" s="17"/>
     </row>
     <row r="616" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B616" t="s">
+      <c r="B616" s="16" t="s">
         <v>196</v>
       </c>
+      <c r="C616" s="9"/>
+      <c r="D616" s="9"/>
+      <c r="E616" s="9"/>
+      <c r="F616" s="17"/>
+    </row>
+    <row r="617" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B617" s="18"/>
+      <c r="C617" s="19"/>
+      <c r="D617" s="19"/>
+      <c r="E617" s="19"/>
+      <c r="F617" s="20"/>
     </row>
     <row r="618" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C618" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="619" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D619" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="621" spans="2:9" x14ac:dyDescent="0.3">
@@ -46206,72 +47685,72 @@
       </c>
     </row>
     <row r="622" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="D622" s="66" t="s">
+      <c r="D622" s="65" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="623" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D623" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="I623" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="624" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D624" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="I624" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="625" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="D625" s="66" t="s">
-        <v>1716</v>
+      <c r="D625" s="65" t="s">
+        <v>1714</v>
       </c>
       <c r="H625" t="s">
         <v>557</v>
       </c>
       <c r="I625" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="626" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="D626" s="66" t="s">
-        <v>1717</v>
+      <c r="D626" s="65" t="s">
+        <v>1715</v>
       </c>
       <c r="H626" t="s">
         <v>557</v>
       </c>
       <c r="I626" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="627" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="D627" s="66" t="s">
-        <v>1718</v>
+      <c r="D627" s="65" t="s">
+        <v>1716</v>
       </c>
       <c r="I627" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="628" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="D628" s="66" t="s">
+      <c r="D628" s="65" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="630" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C630" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="I630" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="631" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D631" s="9" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="E631" s="9"/>
       <c r="F631" s="9"/>
@@ -46282,7 +47761,7 @@
     </row>
     <row r="632" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D632" s="9" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="E632" s="9"/>
       <c r="F632" s="9"/>
@@ -46293,7 +47772,7 @@
     </row>
     <row r="633" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D633" s="9" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="E633" s="9"/>
       <c r="F633" s="9"/>
@@ -46313,7 +47792,7 @@
     </row>
     <row r="635" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D635" s="9" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="E635" s="9"/>
       <c r="F635" s="9"/>
@@ -46342,7 +47821,7 @@
     </row>
     <row r="638" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D638" s="9" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="E638" s="9"/>
       <c r="F638" s="9"/>
@@ -46353,205 +47832,205 @@
     </row>
     <row r="640" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C640" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="641" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D641" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="643" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C643" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="G643" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="644" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D644" s="66" t="s">
-        <v>1720</v>
+      <c r="D644" s="65" t="s">
+        <v>1718</v>
       </c>
     </row>
     <row r="645" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D645" s="25" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="647" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C647" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="648" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D648" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="650" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C650" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="651" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D651" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="653" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C653" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="654" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D654" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="656" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C656" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="657" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D657" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="659" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C659" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="660" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D660" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="662" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C662" s="3" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="663" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C663" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="664" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C664" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="666" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C666" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="667" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D667" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="668" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D668" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="669" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D669" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="670" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D670" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="672" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C672" s="3" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="673" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C673" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="674" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D674" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="675" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D675" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="676" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D676" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="677" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D677" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="678" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D678" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="680" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C680" s="3" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="681" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C681" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="682" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D682" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="683" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D683" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="684" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E684" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="685" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C685" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="686" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D686" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="687" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E687" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="688" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D688" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="689" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E689" s="64" t="s">
-        <v>1599</v>
+      <c r="E689" s="63" t="s">
+        <v>1597</v>
       </c>
     </row>
     <row r="690" spans="3:10" x14ac:dyDescent="0.3">
@@ -46566,85 +48045,85 @@
     </row>
     <row r="692" spans="3:10" x14ac:dyDescent="0.3">
       <c r="E692" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="693" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C693" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="694" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D694" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="695" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D695" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="696" spans="3:10" ht="15" x14ac:dyDescent="0.35">
-      <c r="D696" s="65" t="s">
-        <v>1604</v>
+      <c r="D696" s="64" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="697" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C697" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="698" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D698" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="699" spans="3:10" x14ac:dyDescent="0.3">
       <c r="E699" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="700" spans="3:10" x14ac:dyDescent="0.3">
       <c r="E700" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="701" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E701" s="64" t="s">
-        <v>1609</v>
+      <c r="E701" s="63" t="s">
+        <v>1607</v>
       </c>
     </row>
     <row r="702" spans="3:10" x14ac:dyDescent="0.3">
       <c r="E702" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="J702" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="703" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E703" s="64" t="s">
-        <v>1529</v>
+      <c r="E703" s="63" t="s">
+        <v>1527</v>
       </c>
     </row>
     <row r="705" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D705" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="706" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E706" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="707" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E707" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="709" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E709" s="26" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="F709" s="14"/>
       <c r="G709" s="14"/>
@@ -46654,7 +48133,7 @@
     </row>
     <row r="710" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E710" s="16" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="F710" s="9"/>
       <c r="G710" s="9"/>
@@ -46664,7 +48143,7 @@
     </row>
     <row r="711" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E711" s="18" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="F711" s="19"/>
       <c r="G711" s="19"/>
@@ -46674,53 +48153,53 @@
     </row>
     <row r="713" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E713" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="714" spans="4:10" x14ac:dyDescent="0.3">
       <c r="F714" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="716" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D716" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="717" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E717" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="718" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E718" s="8" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="719" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="E719" s="63" t="s">
         <v>1621</v>
       </c>
-    </row>
-    <row r="719" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="E719" s="64" t="s">
-        <v>1623</v>
-      </c>
       <c r="J719" s="7" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="720" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E720" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="722" spans="4:11" x14ac:dyDescent="0.3">
       <c r="D722" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="K722" s="7" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="723" spans="4:11" x14ac:dyDescent="0.3">
       <c r="E723" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="724" spans="4:11" x14ac:dyDescent="0.3">
@@ -46729,13 +48208,13 @@
       </c>
     </row>
     <row r="725" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="E725" s="64" t="s">
-        <v>1628</v>
+      <c r="E725" s="63" t="s">
+        <v>1626</v>
       </c>
     </row>
     <row r="726" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="E726" s="64" t="s">
-        <v>1627</v>
+      <c r="E726" s="63" t="s">
+        <v>1625</v>
       </c>
     </row>
     <row r="727" spans="4:11" x14ac:dyDescent="0.3">
@@ -46745,7 +48224,7 @@
     </row>
     <row r="729" spans="4:11" x14ac:dyDescent="0.3">
       <c r="E729" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="730" spans="4:11" x14ac:dyDescent="0.3">
@@ -46755,22 +48234,22 @@
     </row>
     <row r="731" spans="4:11" x14ac:dyDescent="0.3">
       <c r="E731" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="732" spans="4:11" x14ac:dyDescent="0.3">
       <c r="E732" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="733" spans="4:11" x14ac:dyDescent="0.3">
       <c r="E733" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="734" spans="4:11" x14ac:dyDescent="0.3">
       <c r="E734" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="735" spans="4:11" x14ac:dyDescent="0.3">
@@ -46780,32 +48259,32 @@
     </row>
     <row r="737" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D737" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="738" spans="3:9" x14ac:dyDescent="0.3">
       <c r="E738" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="739" spans="3:9" x14ac:dyDescent="0.3">
       <c r="E739" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="741" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C741" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="742" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D742" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="743" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D743" s="26" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E743" s="14"/>
       <c r="F743" s="14"/>
@@ -46815,7 +48294,7 @@
     </row>
     <row r="744" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D744" s="16" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="E744" s="9"/>
       <c r="F744" s="9"/>
@@ -46825,7 +48304,7 @@
     </row>
     <row r="745" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D745" s="16" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="E745" s="9"/>
       <c r="F745" s="9"/>
@@ -46835,7 +48314,7 @@
     </row>
     <row r="746" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D746" s="16" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="E746" s="9"/>
       <c r="F746" s="9"/>
@@ -46845,7 +48324,7 @@
     </row>
     <row r="747" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D747" s="16" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="E747" s="9"/>
       <c r="F747" s="9"/>
@@ -46855,7 +48334,7 @@
     </row>
     <row r="748" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D748" s="16" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="E748" s="9"/>
       <c r="F748" s="9"/>
@@ -46865,7 +48344,7 @@
     </row>
     <row r="749" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D749" s="18" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="E749" s="19"/>
       <c r="F749" s="19"/>
@@ -46875,43 +48354,43 @@
     </row>
     <row r="751" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D751" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="753" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D753" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="J753" s="7" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="754" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="D754" s="72" t="s">
-        <v>1845</v>
+      <c r="D754" s="71" t="s">
+        <v>1843</v>
       </c>
       <c r="J754" s="7" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="755" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D755" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="757" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D757" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="758" spans="3:10" x14ac:dyDescent="0.3">
       <c r="E758" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="761" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C761" s="3" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="762" spans="3:10" x14ac:dyDescent="0.3">
@@ -46919,74 +48398,74 @@
         <v>1377</v>
       </c>
       <c r="F762" s="3" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="763" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C763" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="F763" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="764" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C764" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="F764" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="765" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C765" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="F765" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="766" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C766" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F766" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="767" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C767" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="F767" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="768" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C768" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F768" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="769" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C769" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="F769" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="771" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C771" s="3" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="772" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C772" s="3"/>
-      <c r="D772" s="64" t="s">
-        <v>1656</v>
+      <c r="D772" s="63" t="s">
+        <v>1654</v>
       </c>
     </row>
     <row r="773" spans="3:6" x14ac:dyDescent="0.3">
@@ -46995,13 +48474,13 @@
     <row r="774" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C774" s="3"/>
       <c r="D774" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="775" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C775" s="3"/>
       <c r="D775" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="776" spans="3:6" x14ac:dyDescent="0.3">
@@ -47010,29 +48489,29 @@
     <row r="777" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C777" s="3"/>
       <c r="D777" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="778" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C778" s="3"/>
-      <c r="E778" s="64" t="s">
-        <v>1656</v>
+      <c r="E778" s="63" t="s">
+        <v>1654</v>
       </c>
     </row>
     <row r="779" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C779" s="3"/>
-      <c r="E779" s="64"/>
+      <c r="E779" s="63"/>
     </row>
     <row r="780" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C780" s="3"/>
       <c r="E780" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="781" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C781" s="3"/>
       <c r="F781" s="2" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="782" spans="3:6" x14ac:dyDescent="0.3">
@@ -47041,62 +48520,62 @@
     <row r="783" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C783" s="3"/>
       <c r="E783" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="784" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F784" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="786" spans="3:6" x14ac:dyDescent="0.3">
       <c r="E786" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="787" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F787" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="788" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F788" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="789" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F789" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="790" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F790" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="792" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C792" s="3" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="793" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D793" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="795" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D795" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="796" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D796" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="797" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D797" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="798" spans="3:6" x14ac:dyDescent="0.3">
@@ -47106,7 +48585,7 @@
     </row>
     <row r="800" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D800" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="801" spans="4:5" x14ac:dyDescent="0.3">
@@ -47116,27 +48595,27 @@
     </row>
     <row r="802" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E802" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="803" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E803" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="804" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E804" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="805" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E805" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="806" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E806" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="807" spans="4:5" x14ac:dyDescent="0.3">
@@ -47146,57 +48625,57 @@
     </row>
     <row r="809" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D809" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="810" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="E810" s="64" t="s">
-        <v>1681</v>
+      <c r="E810" s="63" t="s">
+        <v>1679</v>
       </c>
     </row>
     <row r="812" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E812" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="813" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E813" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="814" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E814" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="816" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E816" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="818" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="F818" s="64" t="s">
-        <v>1686</v>
+      <c r="F818" s="63" t="s">
+        <v>1684</v>
       </c>
     </row>
     <row r="819" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F819" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="820" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F820" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="821" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F821" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="822" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F822" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="823" spans="3:6" x14ac:dyDescent="0.3">
@@ -47206,25 +48685,25 @@
     </row>
     <row r="824" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C824" s="3" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="825" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C825" s="3"/>
       <c r="D825" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="826" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C826" s="3"/>
       <c r="D826" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="827" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C827" s="3"/>
       <c r="D827" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="828" spans="3:6" x14ac:dyDescent="0.3">
@@ -47233,24 +48712,24 @@
     <row r="829" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C829" s="3"/>
       <c r="D829" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="830" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C830" s="3"/>
       <c r="E830" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="831" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C831" s="3"/>
       <c r="E831" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="834" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C834" s="3" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="835" spans="3:5" x14ac:dyDescent="0.3">
@@ -47258,44 +48737,44 @@
     </row>
     <row r="836" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C836" s="3"/>
-      <c r="D836" s="69" t="s">
+      <c r="D836" s="68" t="s">
         <v>1215</v>
       </c>
     </row>
     <row r="837" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C837" s="3"/>
-      <c r="D837" s="67" t="s">
-        <v>1736</v>
+      <c r="D837" s="66" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="838" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C838" s="3"/>
       <c r="E838" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="839" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C839" s="3"/>
       <c r="E839" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="840" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C840" s="3"/>
       <c r="E840" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="841" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C841" s="3"/>
       <c r="E841" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="842" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C842" s="3"/>
       <c r="E842" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="843" spans="3:5" x14ac:dyDescent="0.3">
@@ -47303,32 +48782,32 @@
     </row>
     <row r="844" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C844" s="3"/>
-      <c r="D844" s="68" t="s">
-        <v>1735</v>
+      <c r="D844" s="67" t="s">
+        <v>1733</v>
       </c>
     </row>
     <row r="845" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C845" s="3"/>
       <c r="D845" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="846" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C846" s="3"/>
       <c r="E846" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="847" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C847" s="3"/>
       <c r="E847" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="848" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C848" s="3"/>
       <c r="E848" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="849" spans="3:10" x14ac:dyDescent="0.3">
@@ -47337,7 +48816,7 @@
     <row r="850" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C850" s="3"/>
       <c r="D850" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="851" spans="3:10" x14ac:dyDescent="0.3">
@@ -47345,8 +48824,8 @@
     </row>
     <row r="852" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C852" s="3"/>
-      <c r="D852" s="67" t="s">
-        <v>1742</v>
+      <c r="D852" s="66" t="s">
+        <v>1740</v>
       </c>
     </row>
     <row r="853" spans="3:10" x14ac:dyDescent="0.3">
@@ -47354,30 +48833,30 @@
     </row>
     <row r="854" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C854" s="3"/>
-      <c r="E854" s="67" t="s">
-        <v>1743</v>
+      <c r="E854" s="66" t="s">
+        <v>1741</v>
       </c>
     </row>
     <row r="855" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C855" s="3"/>
       <c r="E855" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="856" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C856" s="3"/>
       <c r="E856" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="857" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C857" s="3"/>
       <c r="E857" s="13" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="F857" s="15"/>
       <c r="G857" s="13" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="H857" s="14"/>
       <c r="I857" s="14"/>
@@ -47386,11 +48865,11 @@
     <row r="858" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C858" s="3"/>
       <c r="E858" s="21" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="F858" s="23"/>
       <c r="G858" s="21" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="H858" s="22"/>
       <c r="I858" s="22"/>
@@ -47399,11 +48878,11 @@
     <row r="859" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C859" s="3"/>
       <c r="E859" s="16" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="F859" s="17"/>
       <c r="G859" s="16" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="H859" s="9"/>
       <c r="I859" s="9"/>
@@ -47416,7 +48895,7 @@
       </c>
       <c r="F860" s="23"/>
       <c r="G860" s="21" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="H860" s="22"/>
       <c r="I860" s="22"/>
@@ -47425,11 +48904,11 @@
     <row r="861" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C861" s="3"/>
       <c r="E861" s="18" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="F861" s="20"/>
       <c r="G861" s="18" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="H861" s="19"/>
       <c r="I861" s="19"/>
@@ -47440,24 +48919,24 @@
     </row>
     <row r="863" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C863" s="3"/>
-      <c r="E863" s="67" t="s">
-        <v>1754</v>
+      <c r="E863" s="66" t="s">
+        <v>1752</v>
       </c>
     </row>
     <row r="864" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C864" s="3"/>
       <c r="E864" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="865" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C865" s="3"/>
       <c r="E865" s="13" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="F865" s="15"/>
       <c r="G865" s="13" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="H865" s="14"/>
       <c r="I865" s="14"/>
@@ -47466,11 +48945,11 @@
     <row r="866" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C866" s="3"/>
       <c r="E866" s="21" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="F866" s="23"/>
       <c r="G866" s="21" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="H866" s="22"/>
       <c r="I866" s="22"/>
@@ -47479,11 +48958,11 @@
     <row r="867" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C867" s="3"/>
       <c r="E867" s="16" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="F867" s="17"/>
       <c r="G867" s="16" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="H867" s="9"/>
       <c r="I867" s="9"/>
@@ -47492,11 +48971,11 @@
     <row r="868" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C868" s="3"/>
       <c r="E868" s="21" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="F868" s="23"/>
       <c r="G868" s="21" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="H868" s="22"/>
       <c r="I868" s="22"/>
@@ -47505,11 +48984,11 @@
     <row r="869" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C869" s="3"/>
       <c r="E869" s="16" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="F869" s="17"/>
       <c r="G869" s="16" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="H869" s="9"/>
       <c r="I869" s="9"/>
@@ -47518,11 +48997,11 @@
     <row r="870" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C870" s="3"/>
       <c r="E870" s="21" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="F870" s="23"/>
       <c r="G870" s="21" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="H870" s="22"/>
       <c r="I870" s="22"/>
@@ -47533,13 +49012,13 @@
     </row>
     <row r="872" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D872" s="3" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="873" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D873" s="3"/>
-      <c r="E873" s="67" t="s">
-        <v>1768</v>
+      <c r="E873" s="66" t="s">
+        <v>1766</v>
       </c>
     </row>
     <row r="874" spans="3:10" x14ac:dyDescent="0.3">
@@ -47548,33 +49027,33 @@
     <row r="875" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D875" s="3"/>
       <c r="E875" s="13" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="F875" s="15"/>
       <c r="G875" s="13" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="H875" s="15"/>
     </row>
     <row r="876" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D876" s="3"/>
       <c r="E876" s="21" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="F876" s="23"/>
       <c r="G876" s="21" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="H876" s="23"/>
     </row>
     <row r="877" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D877" s="3"/>
       <c r="E877" s="16" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="F877" s="17"/>
       <c r="G877" s="16" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="H877" s="17"/>
     </row>
@@ -47585,29 +49064,29 @@
       </c>
       <c r="F878" s="23"/>
       <c r="G878" s="21" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="H878" s="23"/>
     </row>
     <row r="879" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D879" s="3"/>
       <c r="E879" s="16" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="F879" s="17"/>
       <c r="G879" s="16" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="H879" s="17"/>
     </row>
     <row r="880" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D880" s="3"/>
       <c r="E880" s="21" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="F880" s="23"/>
       <c r="G880" s="21" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="H880" s="23"/>
     </row>
@@ -47616,14 +49095,14 @@
     </row>
     <row r="882" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D882" s="3"/>
-      <c r="E882" s="67" t="s">
-        <v>1776</v>
+      <c r="E882" s="66" t="s">
+        <v>1774</v>
       </c>
     </row>
     <row r="883" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D883" s="3"/>
       <c r="E883" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="884" spans="4:10" x14ac:dyDescent="0.3">
@@ -47632,11 +49111,11 @@
     <row r="885" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D885" s="3"/>
       <c r="E885" s="13" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="F885" s="14"/>
       <c r="G885" s="13" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="H885" s="14"/>
       <c r="I885" s="14"/>
@@ -47645,7 +49124,7 @@
     <row r="886" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D886" s="3"/>
       <c r="E886" s="21" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="F886" s="23"/>
       <c r="G886" s="21" t="s">
@@ -47658,11 +49137,11 @@
     <row r="887" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D887" s="3"/>
       <c r="E887" s="16" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="F887" s="9"/>
       <c r="G887" s="16" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="H887" s="9"/>
       <c r="I887" s="9"/>
@@ -47671,11 +49150,11 @@
     <row r="888" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D888" s="3"/>
       <c r="E888" s="21" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="F888" s="23"/>
       <c r="G888" s="21" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="H888" s="22"/>
       <c r="I888" s="22"/>
@@ -47684,11 +49163,11 @@
     <row r="889" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D889" s="3"/>
       <c r="E889" s="18" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="F889" s="19"/>
       <c r="G889" s="16" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="H889" s="9"/>
       <c r="I889" s="9"/>
@@ -47697,11 +49176,11 @@
     <row r="890" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D890" s="3"/>
       <c r="E890" s="21" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="F890" s="23"/>
       <c r="G890" s="21" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="H890" s="22"/>
       <c r="I890" s="22"/>
@@ -47712,25 +49191,25 @@
     </row>
     <row r="892" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D892" s="3" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="893" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D893" s="3"/>
-      <c r="E893" s="67" t="s">
-        <v>1784</v>
+      <c r="E893" s="66" t="s">
+        <v>1782</v>
       </c>
     </row>
     <row r="894" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D894" s="3"/>
       <c r="E894" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="895" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D895" s="3"/>
       <c r="E895" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="896" spans="4:10" x14ac:dyDescent="0.3">
@@ -47739,7 +49218,7 @@
     <row r="897" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D897" s="3"/>
       <c r="E897" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="898" spans="4:5" x14ac:dyDescent="0.3">
@@ -47747,221 +49226,221 @@
     </row>
     <row r="899" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D899" s="3" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="900" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D900" s="3"/>
       <c r="E900" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="901" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D901" s="3"/>
       <c r="E901" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="902" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D902" s="3"/>
       <c r="E902" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="903" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D903" s="3"/>
       <c r="E903" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="904" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D904" s="3"/>
       <c r="E904" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="905" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D905" s="3"/>
       <c r="E905" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="906" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D906" s="3"/>
       <c r="E906" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="907" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D907" s="3"/>
       <c r="E907" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="908" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D908" s="3"/>
       <c r="E908" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="909" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D909" s="3"/>
       <c r="E909" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="910" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D910" s="3"/>
       <c r="E910" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="911" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E911" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="913" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C913" s="3" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="914" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D914" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="H914" s="9" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="915" spans="3:8" x14ac:dyDescent="0.3">
       <c r="H915" s="9" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="916" spans="3:8" x14ac:dyDescent="0.3">
       <c r="H916" s="9" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="917" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D917" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="918" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E918" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="919" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D919" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="920" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="E920" s="72" t="s">
-        <v>1811</v>
+      <c r="E920" s="71" t="s">
+        <v>1809</v>
       </c>
     </row>
     <row r="922" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D922" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="923" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E923" s="2" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="924" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E924" s="2" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="926" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D926" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="927" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E927" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="928" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E928" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="930" spans="4:8" x14ac:dyDescent="0.3">
       <c r="E930" s="2" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="932" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D932" s="3" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="933" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D933" s="3"/>
       <c r="E933" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="934" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D934" s="3"/>
       <c r="E934" s="13" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="F934" s="15"/>
       <c r="G934" s="13" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="H934" s="15"/>
     </row>
     <row r="935" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D935" s="3"/>
-      <c r="E935" s="73" t="s">
-        <v>1826</v>
+      <c r="E935" s="72" t="s">
+        <v>1824</v>
       </c>
       <c r="F935" s="23"/>
       <c r="G935" s="21" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="H935" s="23"/>
     </row>
     <row r="936" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D936" s="3"/>
-      <c r="E936" s="74" t="s">
-        <v>1827</v>
+      <c r="E936" s="73" t="s">
+        <v>1825</v>
       </c>
       <c r="F936" s="17"/>
       <c r="G936" s="16" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="H936" s="17"/>
     </row>
     <row r="937" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D937" s="3"/>
-      <c r="E937" s="73" t="s">
-        <v>1828</v>
+      <c r="E937" s="72" t="s">
+        <v>1826</v>
       </c>
       <c r="F937" s="23"/>
       <c r="G937" s="21" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="H937" s="23"/>
     </row>
     <row r="938" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D938" s="3"/>
       <c r="E938" s="18" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="F938" s="20"/>
       <c r="G938" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="H938" s="20"/>
     </row>
@@ -47970,92 +49449,92 @@
     </row>
     <row r="940" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D940" s="3"/>
-      <c r="E940" s="75" t="s">
-        <v>1830</v>
+      <c r="E940" s="74" t="s">
+        <v>1828</v>
       </c>
     </row>
     <row r="941" spans="4:8" x14ac:dyDescent="0.3">
       <c r="F941" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="942" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="F942" s="72" t="s">
-        <v>1832</v>
+      <c r="F942" s="71" t="s">
+        <v>1830</v>
       </c>
     </row>
     <row r="943" spans="4:8" x14ac:dyDescent="0.3">
       <c r="E943" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="944" spans="4:8" x14ac:dyDescent="0.3">
       <c r="F944" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="946" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D946" s="3" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="947" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D947" s="3"/>
       <c r="E947" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="948" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D948" s="3"/>
       <c r="F948" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="949" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D949" s="3"/>
       <c r="F949" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="950" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D950" s="3"/>
       <c r="F950" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="951" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D951" s="3"/>
       <c r="E951" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="952" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D952" s="3" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="953" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D953" s="3"/>
       <c r="E953" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="954" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D954" s="3"/>
       <c r="E954" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="955" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D955" s="3"/>
       <c r="E955" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="956" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D956" s="3"/>
       <c r="E956" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="957" spans="3:6" x14ac:dyDescent="0.3">
@@ -48063,122 +49542,122 @@
     </row>
     <row r="958" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C958" s="3" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="D958" s="3"/>
     </row>
     <row r="959" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C959" s="3"/>
-      <c r="D959" s="72" t="s">
-        <v>1847</v>
+      <c r="D959" s="71" t="s">
+        <v>1845</v>
       </c>
     </row>
     <row r="960" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C960" s="3"/>
-      <c r="D960" s="72" t="s">
-        <v>1848</v>
+      <c r="D960" s="71" t="s">
+        <v>1846</v>
       </c>
     </row>
     <row r="961" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C961" s="3"/>
-      <c r="D961" s="72"/>
+      <c r="D961" s="71"/>
       <c r="E961" s="3" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="962" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C962" s="3"/>
-      <c r="D962" s="72"/>
+      <c r="D962" s="71"/>
       <c r="E962" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="963" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C963" s="3"/>
-      <c r="D963" s="72"/>
+      <c r="D963" s="71"/>
     </row>
     <row r="964" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C964" s="3"/>
-      <c r="D964" s="72"/>
+      <c r="D964" s="71"/>
       <c r="E964" s="3" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="965" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C965" s="3"/>
-      <c r="D965" s="72"/>
+      <c r="D965" s="71"/>
       <c r="E965" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="966" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C966" s="3"/>
-      <c r="D966" s="72"/>
+      <c r="D966" s="71"/>
       <c r="E966" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="967" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C967" s="3"/>
-      <c r="D967" s="72"/>
+      <c r="D967" s="71"/>
     </row>
     <row r="968" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C968" s="3"/>
-      <c r="D968" s="72"/>
+      <c r="D968" s="71"/>
       <c r="E968" s="3" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="969" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C969" s="3"/>
-      <c r="D969" s="72"/>
+      <c r="D969" s="71"/>
       <c r="E969" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="970" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C970" s="3"/>
-      <c r="D970" s="72"/>
+      <c r="D970" s="71"/>
     </row>
     <row r="971" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C971" s="3"/>
       <c r="D971" s="3" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="972" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C972" s="3"/>
       <c r="D972" s="3"/>
       <c r="E972" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="973" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C973" s="3"/>
       <c r="D973" s="3"/>
       <c r="E973" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="974" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C974" s="3"/>
       <c r="D974" s="3"/>
       <c r="F974" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="975" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C975" s="3"/>
       <c r="D975" s="3"/>
       <c r="E975" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="976" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C976" s="3"/>
       <c r="D976" s="3"/>
       <c r="F976" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="977" spans="3:7" x14ac:dyDescent="0.3">
@@ -48187,126 +49666,126 @@
     </row>
     <row r="978" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C978" s="3"/>
-      <c r="D978" s="72"/>
+      <c r="D978" s="71"/>
       <c r="E978" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="979" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D979" s="71"/>
+      <c r="F979" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="980" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D980" s="71"/>
+      <c r="F980" t="s">
         <v>1862</v>
       </c>
     </row>
-    <row r="979" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D979" s="72"/>
-      <c r="F979" t="s">
+    <row r="981" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D981" s="71"/>
+      <c r="F981" t="s">
         <v>1863</v>
       </c>
     </row>
-    <row r="980" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D980" s="72"/>
-      <c r="F980" t="s">
+    <row r="982" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D982" s="71"/>
+      <c r="F982" t="s">
         <v>1864</v>
       </c>
     </row>
-    <row r="981" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D981" s="72"/>
-      <c r="F981" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="982" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D982" s="72"/>
-      <c r="F982" t="s">
-        <v>1866</v>
-      </c>
-    </row>
     <row r="983" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D983" s="72"/>
+      <c r="D983" s="71"/>
     </row>
     <row r="984" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D984" s="3" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="985" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D985" s="71"/>
+      <c r="E985" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="986" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D986" s="71"/>
+      <c r="F986" t="s">
         <v>1867</v>
       </c>
     </row>
-    <row r="985" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D985" s="72"/>
-      <c r="E985" t="s">
+    <row r="987" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D987" s="71"/>
+    </row>
+    <row r="988" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D988" s="71"/>
+      <c r="F988" t="s">
         <v>1868</v>
       </c>
     </row>
-    <row r="986" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D986" s="72"/>
-      <c r="F986" t="s">
+    <row r="989" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D989" s="71"/>
+      <c r="F989" t="s">
         <v>1869</v>
       </c>
     </row>
-    <row r="987" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D987" s="72"/>
-    </row>
-    <row r="988" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D988" s="72"/>
-      <c r="F988" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="989" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D989" s="72"/>
-      <c r="F989" t="s">
-        <v>1871</v>
-      </c>
-    </row>
     <row r="990" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D990" s="72"/>
+      <c r="D990" s="71"/>
     </row>
     <row r="991" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D991" s="3" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="992" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D992" s="72"/>
+      <c r="D992" s="71"/>
       <c r="E992" s="3" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G992" s="3" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="993" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D993" s="71"/>
+      <c r="E993" t="s">
         <v>1872</v>
       </c>
-      <c r="G992" s="3" t="s">
+      <c r="G993" t="s">
         <v>1873</v>
       </c>
     </row>
-    <row r="993" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D993" s="72"/>
-      <c r="E993" t="s">
+    <row r="994" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D994" s="71"/>
+      <c r="E994" t="s">
         <v>1874</v>
       </c>
-      <c r="G993" t="s">
+      <c r="G994" t="s">
         <v>1875</v>
       </c>
     </row>
-    <row r="994" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D994" s="72"/>
-      <c r="E994" t="s">
+    <row r="995" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D995" s="71"/>
+      <c r="E995" t="s">
         <v>1876</v>
       </c>
-      <c r="G994" t="s">
+      <c r="G995" t="s">
         <v>1877</v>
       </c>
     </row>
-    <row r="995" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D995" s="72"/>
-      <c r="E995" t="s">
-        <v>1878</v>
-      </c>
-      <c r="G995" t="s">
-        <v>1879</v>
-      </c>
-    </row>
     <row r="996" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D996" s="72"/>
+      <c r="D996" s="71"/>
     </row>
     <row r="997" spans="2:7" x14ac:dyDescent="0.3">
       <c r="D997" s="3" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="998" spans="2:7" x14ac:dyDescent="0.3">
       <c r="D998" s="3"/>
       <c r="E998" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="999" spans="2:7" x14ac:dyDescent="0.3">
@@ -48316,7 +49795,7 @@
       <c r="D1000" s="3"/>
     </row>
     <row r="1001" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D1001" s="72"/>
+      <c r="D1001" s="71"/>
     </row>
     <row r="1002" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B1002" t="s">
@@ -48379,18 +49858,18 @@
         <v>1425</v>
       </c>
       <c r="H1014" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="J1014" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1015" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H1015" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J1015" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1016" spans="1:10" x14ac:dyDescent="0.3">
@@ -48703,7 +50182,7 @@
       <c r="C1083" t="s">
         <v>476</v>
       </c>
-      <c r="G1083" s="37" t="s">
+      <c r="G1083" s="78" t="s">
         <v>1180</v>
       </c>
       <c r="J1083" t="s">
@@ -48922,7 +50401,7 @@
       <c r="G1102" s="42" t="s">
         <v>1241</v>
       </c>
-      <c r="J1102" s="51" t="s">
+      <c r="J1102" s="50" t="s">
         <v>1222</v>
       </c>
       <c r="K1102" s="27" t="s">
@@ -48987,7 +50466,7 @@
       <c r="J1105" s="41" t="s">
         <v>1225</v>
       </c>
-      <c r="K1105" s="49" t="s">
+      <c r="K1105" s="80" t="s">
         <v>1234</v>
       </c>
       <c r="L1105" s="24"/>
@@ -49000,7 +50479,7 @@
       <c r="J1106" s="41" t="s">
         <v>398</v>
       </c>
-      <c r="K1106" s="49" t="s">
+      <c r="K1106" s="80" t="s">
         <v>1235</v>
       </c>
       <c r="L1106" s="24"/>
@@ -49013,7 +50492,7 @@
       <c r="I1107" t="s">
         <v>557</v>
       </c>
-      <c r="K1107" s="50"/>
+      <c r="K1107" s="49"/>
       <c r="L1107" s="9"/>
       <c r="M1107" s="9"/>
       <c r="N1107" s="9"/>
@@ -49129,784 +50608,1905 @@
         <v>1229</v>
       </c>
     </row>
+    <row r="1127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1127" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1128" s="76" t="s">
+        <v>1899</v>
+      </c>
+    </row>
     <row r="1129" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1129" s="62" t="s">
+      <c r="C1129" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1130" s="76" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C1131" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C1132" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D1133" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D1134" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1136" s="76" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="1137" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1137" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="1139" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1139" s="26" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C1139" s="14"/>
+      <c r="D1139" s="14"/>
+      <c r="E1139" s="14"/>
+      <c r="F1139" s="14"/>
+      <c r="G1139" s="15"/>
+      <c r="I1139" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="J1139" s="14"/>
+      <c r="K1139" s="14"/>
+      <c r="L1139" s="14"/>
+      <c r="M1139" s="14"/>
+      <c r="N1139" s="14"/>
+      <c r="O1139" s="15"/>
+    </row>
+    <row r="1140" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1140" s="16" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C1140" s="9"/>
+      <c r="D1140" s="9"/>
+      <c r="E1140" s="9"/>
+      <c r="F1140" s="9"/>
+      <c r="G1140" s="17"/>
+      <c r="I1140" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="J1140" s="9"/>
+      <c r="K1140" s="9"/>
+      <c r="L1140" s="9"/>
+      <c r="M1140" s="9"/>
+      <c r="N1140" s="9"/>
+      <c r="O1140" s="17"/>
+    </row>
+    <row r="1141" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1141" s="16" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C1141" s="9"/>
+      <c r="D1141" s="9"/>
+      <c r="E1141" s="9"/>
+      <c r="F1141" s="9"/>
+      <c r="G1141" s="17"/>
+      <c r="I1141" s="16" t="s">
+        <v>1187</v>
+      </c>
+      <c r="J1141" s="9"/>
+      <c r="K1141" s="9"/>
+      <c r="L1141" s="9"/>
+      <c r="M1141" s="9"/>
+      <c r="N1141" s="9"/>
+      <c r="O1141" s="17"/>
+    </row>
+    <row r="1142" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1142" s="16" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C1142" s="9"/>
+      <c r="D1142" s="9"/>
+      <c r="E1142" s="9"/>
+      <c r="F1142" s="9"/>
+      <c r="G1142" s="17"/>
+      <c r="I1142" s="16" t="s">
+        <v>1176</v>
+      </c>
+      <c r="J1142" s="9"/>
+      <c r="K1142" s="9"/>
+      <c r="L1142" s="9"/>
+      <c r="M1142" s="9"/>
+      <c r="N1142" s="9"/>
+      <c r="O1142" s="17"/>
+    </row>
+    <row r="1143" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1143" s="16" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C1143" s="9"/>
+      <c r="D1143" s="9"/>
+      <c r="E1143" s="9"/>
+      <c r="F1143" s="9"/>
+      <c r="G1143" s="17"/>
+      <c r="I1143" s="16" t="s">
+        <v>928</v>
+      </c>
+      <c r="J1143" s="9"/>
+      <c r="K1143" s="9"/>
+      <c r="L1143" s="9"/>
+      <c r="M1143" s="9"/>
+      <c r="N1143" s="9"/>
+      <c r="O1143" s="17"/>
+      <c r="P1143" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="1144" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1144" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="C1144" s="9"/>
+      <c r="D1144" s="9"/>
+      <c r="E1144" s="9"/>
+      <c r="F1144" s="9"/>
+      <c r="G1144" s="17"/>
+      <c r="I1144" s="16" t="s">
+        <v>929</v>
+      </c>
+      <c r="J1144" s="9"/>
+      <c r="K1144" s="9"/>
+      <c r="L1144" s="9"/>
+      <c r="M1144" s="9"/>
+      <c r="N1144" s="9"/>
+      <c r="O1144" s="17"/>
+      <c r="Q1144" t="s">
+        <v>1921</v>
+      </c>
+      <c r="T1144" s="51" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1145" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1145" s="16"/>
+      <c r="C1145" s="9"/>
+      <c r="D1145" s="9"/>
+      <c r="E1145" s="9"/>
+      <c r="F1145" s="9"/>
+      <c r="G1145" s="17"/>
+      <c r="I1145" s="16" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J1145" s="9"/>
+      <c r="K1145" s="9"/>
+      <c r="L1145" s="9"/>
+      <c r="M1145" s="9"/>
+      <c r="N1145" s="9"/>
+      <c r="O1145" s="17"/>
+    </row>
+    <row r="1146" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1146" s="16" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C1146" s="9"/>
+      <c r="D1146" s="9"/>
+      <c r="E1146" s="9"/>
+      <c r="F1146" s="9"/>
+      <c r="G1146" s="17"/>
+      <c r="I1146" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="J1146" s="9"/>
+      <c r="K1146" s="9"/>
+      <c r="L1146" s="9"/>
+      <c r="M1146" s="9"/>
+      <c r="N1146" s="9"/>
+      <c r="O1146" s="17"/>
+    </row>
+    <row r="1147" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1147" s="16" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C1147" s="9"/>
+      <c r="D1147" s="9"/>
+      <c r="E1147" s="9"/>
+      <c r="F1147" s="9"/>
+      <c r="G1147" s="17"/>
+      <c r="I1147" s="16" t="s">
+        <v>834</v>
+      </c>
+      <c r="J1147" s="9"/>
+      <c r="K1147" s="9"/>
+      <c r="L1147" s="9"/>
+      <c r="M1147" s="9"/>
+      <c r="N1147" s="9"/>
+      <c r="O1147" s="17"/>
+      <c r="Q1147" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="1148" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1148" s="16"/>
+      <c r="C1148" s="9"/>
+      <c r="D1148" s="9"/>
+      <c r="E1148" s="9"/>
+      <c r="F1148" s="9"/>
+      <c r="G1148" s="17"/>
+      <c r="I1148" s="16"/>
+      <c r="J1148" s="9"/>
+      <c r="K1148" s="9"/>
+      <c r="L1148" s="9"/>
+      <c r="M1148" s="9"/>
+      <c r="N1148" s="9"/>
+      <c r="O1148" s="17"/>
+      <c r="Q1148" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="1149" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1149" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1149" s="9"/>
+      <c r="D1149" s="9"/>
+      <c r="E1149" s="9"/>
+      <c r="F1149" s="9"/>
+      <c r="G1149" s="17"/>
+      <c r="I1149" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="J1149" s="9"/>
+      <c r="K1149" s="9"/>
+      <c r="L1149" s="9"/>
+      <c r="M1149" s="9"/>
+      <c r="N1149" s="9"/>
+      <c r="O1149" s="17"/>
+      <c r="T1149" s="51" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="1150" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1150" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="C1150" s="9"/>
+      <c r="D1150" s="9"/>
+      <c r="E1150" s="9"/>
+      <c r="F1150" s="9"/>
+      <c r="G1150" s="17"/>
+      <c r="I1150" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1150" s="9"/>
+      <c r="K1150" s="9"/>
+      <c r="L1150" s="9"/>
+      <c r="M1150" s="9"/>
+      <c r="N1150" s="9"/>
+      <c r="O1150" s="17"/>
+    </row>
+    <row r="1151" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1151" s="16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C1151" s="9"/>
+      <c r="D1151" s="9"/>
+      <c r="E1151" s="9"/>
+      <c r="F1151" s="9"/>
+      <c r="G1151" s="17"/>
+      <c r="I1151" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="J1151" s="19"/>
+      <c r="K1151" s="19"/>
+      <c r="L1151" s="19"/>
+      <c r="M1151" s="19" t="s">
+        <v>1916</v>
+      </c>
+      <c r="N1151" s="19"/>
+      <c r="O1151" s="20"/>
+    </row>
+    <row r="1152" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1152" s="16" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1152" s="9"/>
+      <c r="D1152" s="9"/>
+      <c r="E1152" s="9"/>
+      <c r="F1152" s="9"/>
+      <c r="G1152" s="17"/>
+    </row>
+    <row r="1153" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1153" s="16"/>
+      <c r="C1153" s="9"/>
+      <c r="D1153" s="9"/>
+      <c r="E1153" s="9"/>
+      <c r="F1153" s="9"/>
+      <c r="G1153" s="17"/>
+    </row>
+    <row r="1154" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1154" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="C1154" s="9"/>
+      <c r="D1154" s="9"/>
+      <c r="E1154" s="9"/>
+      <c r="F1154" s="9"/>
+      <c r="G1154" s="17"/>
+    </row>
+    <row r="1155" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1155" s="16" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C1155" s="9"/>
+      <c r="D1155" s="9"/>
+      <c r="E1155" s="9"/>
+      <c r="F1155" s="9"/>
+      <c r="G1155" s="17"/>
+    </row>
+    <row r="1156" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1156" s="18" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C1156" s="19"/>
+      <c r="D1156" s="19"/>
+      <c r="E1156" s="19"/>
+      <c r="F1156" s="19"/>
+      <c r="G1156" s="20"/>
+    </row>
+    <row r="1158" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1158" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="1159" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C1159" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="1160" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C1160" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1161" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1161" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1162" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C1162" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="1163" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C1163" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="1164" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C1164" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="1166" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1166" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="1167" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C1167" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1168" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D1168" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D1169" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D1170" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C1171" s="2" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C1172" s="2"/>
+    </row>
+    <row r="1173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1173" s="76" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C1173" s="2"/>
+      <c r="H1173" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1174" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C1174" s="2"/>
+    </row>
+    <row r="1175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1175" t="s">
+        <v>928</v>
+      </c>
+      <c r="C1175" s="2"/>
+    </row>
+    <row r="1176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1176" t="s">
+        <v>929</v>
+      </c>
+      <c r="C1176" s="2"/>
+      <c r="H1176" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1177" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C1177" s="2"/>
+      <c r="H1177" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1178" t="s">
+        <v>475</v>
+      </c>
+      <c r="C1178" s="2"/>
+    </row>
+    <row r="1179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1179" t="s">
+        <v>834</v>
+      </c>
+      <c r="C1179" s="2"/>
+    </row>
+    <row r="1180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C1180" s="2"/>
+    </row>
+    <row r="1182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1182" s="79" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1183" s="61"/>
+      <c r="B1183" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="1185" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B1185" s="61" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="1186" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B1186" t="s">
         <v>1450</v>
       </c>
     </row>
-    <row r="1130" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1130" s="62"/>
-      <c r="B1130" t="s">
+    <row r="1187" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B1187" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1189" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B1189" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1190" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C1190" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="1192" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C1192" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="1193" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D1193" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="1195" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B1195" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="1196" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C1196" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="1197" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C1197" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="1199" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C1199" s="2" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="1201" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B1201" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="1202" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C1202" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1203" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C1203" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="1204" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D1204" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1206" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C1206" t="s">
         <v>1464</v>
       </c>
     </row>
-    <row r="1132" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B1132" s="62" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="1133" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B1133" t="s">
-        <v>1451</v>
-      </c>
-    </row>
-    <row r="1134" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B1134" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="1136" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B1136" t="s">
-        <v>1452</v>
-      </c>
-    </row>
-    <row r="1137" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1137" t="s">
-        <v>1453</v>
-      </c>
-    </row>
-    <row r="1139" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1139" t="s">
-        <v>1454</v>
-      </c>
-    </row>
-    <row r="1140" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D1140" t="s">
-        <v>1455</v>
-      </c>
-    </row>
-    <row r="1142" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B1142" t="s">
-        <v>1456</v>
-      </c>
-    </row>
-    <row r="1143" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1143" t="s">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="1144" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1144" t="s">
-        <v>1458</v>
-      </c>
-    </row>
-    <row r="1146" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1146" s="2" t="s">
-        <v>1459</v>
-      </c>
-    </row>
-    <row r="1148" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B1148" t="s">
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="1149" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1149" t="s">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="1150" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1150" t="s">
-        <v>1462</v>
-      </c>
-    </row>
-    <row r="1151" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D1151" t="s">
-        <v>1463</v>
-      </c>
-    </row>
-    <row r="1153" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1153" t="s">
+    <row r="1208" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C1208" t="s">
         <v>1465</v>
       </c>
     </row>
-    <row r="1155" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1155" t="s">
+    <row r="1209" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D1209" t="s">
         <v>1466</v>
       </c>
     </row>
-    <row r="1156" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D1156" t="s">
+    <row r="1210" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D1210" s="2" t="s">
         <v>1467</v>
       </c>
     </row>
-    <row r="1157" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D1157" s="2" t="s">
+    <row r="1212" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B1212" t="s">
         <v>1468</v>
       </c>
     </row>
-    <row r="1159" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B1159" t="s">
+    <row r="1213" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C1213" t="s">
         <v>1469</v>
       </c>
     </row>
-    <row r="1160" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1160" t="s">
+    <row r="1214" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C1214" t="s">
         <v>1470</v>
       </c>
     </row>
-    <row r="1161" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1161" t="s">
+    <row r="1215" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C1215" t="s">
         <v>1471</v>
       </c>
     </row>
-    <row r="1162" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1162" t="s">
+    <row r="1216" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F1216" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="1217" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1217" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1218" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1218" s="61" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="1164" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1164" t="s">
+    <row r="1219" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1219" s="61" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1220" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1220" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1221" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1221" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1222" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1222" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1224" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1224" t="s">
         <v>1478</v>
       </c>
     </row>
-    <row r="1165" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1165" s="62" t="s">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="1166" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1166" s="62" t="s">
-        <v>1476</v>
-      </c>
-    </row>
-    <row r="1167" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1167" t="s">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="1168" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C1168" t="s">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="1169" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C1169" t="s">
-        <v>1475</v>
-      </c>
-    </row>
-    <row r="1171" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C1171" t="s">
+    <row r="1225" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D1225" t="s">
         <v>1479</v>
       </c>
     </row>
-    <row r="1172" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="D1172" t="s">
+    <row r="1227" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1227" t="s">
         <v>1480</v>
       </c>
     </row>
-    <row r="1174" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C1174" t="s">
+    <row r="1229" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1229" s="3" t="s">
         <v>1481</v>
       </c>
     </row>
-    <row r="1176" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B1176" s="3" t="s">
+    <row r="1230" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1230" s="11" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D1230" s="13" t="s">
         <v>1482</v>
       </c>
-    </row>
-    <row r="1177" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C1177" s="11" t="s">
+      <c r="E1230" s="15"/>
+      <c r="F1230" s="13" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G1230" s="14"/>
+      <c r="H1230" s="15"/>
+      <c r="I1230" s="13" t="s">
+        <v>1379</v>
+      </c>
+      <c r="J1230" s="14"/>
+      <c r="K1230" s="14"/>
+      <c r="L1230" s="14"/>
+      <c r="M1230" s="15"/>
+    </row>
+    <row r="1231" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1231" s="53">
+        <v>1</v>
+      </c>
+      <c r="D1231" s="16" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E1231" s="17"/>
+      <c r="F1231" s="16" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1231" s="9"/>
+      <c r="H1231" s="17"/>
+      <c r="I1231" s="16" t="s">
+        <v>1486</v>
+      </c>
+      <c r="J1231" s="9"/>
+      <c r="K1231" s="9"/>
+      <c r="L1231" s="9"/>
+      <c r="M1231" s="17"/>
+    </row>
+    <row r="1232" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1232" s="53">
+        <v>2</v>
+      </c>
+      <c r="D1232" s="16" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E1232" s="17"/>
+      <c r="F1232" s="16" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1232" s="9"/>
+      <c r="H1232" s="17"/>
+      <c r="I1232" s="16" t="s">
+        <v>1488</v>
+      </c>
+      <c r="J1232" s="9"/>
+      <c r="K1232" s="9"/>
+      <c r="L1232" s="9"/>
+      <c r="M1232" s="17"/>
+    </row>
+    <row r="1233" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1233" s="53">
+        <v>3</v>
+      </c>
+      <c r="D1233" s="16" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E1233" s="17"/>
+      <c r="F1233" s="29" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G1233" s="9"/>
+      <c r="H1233" s="17"/>
+      <c r="I1233" s="29" t="s">
+        <v>1918</v>
+      </c>
+      <c r="J1233" s="9"/>
+      <c r="K1233" s="9"/>
+      <c r="L1233" s="9"/>
+      <c r="M1233" s="17"/>
+    </row>
+    <row r="1234" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1234" s="53">
+        <v>4</v>
+      </c>
+      <c r="D1234" s="16" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E1234" s="17"/>
+      <c r="F1234" s="16" t="s">
+        <v>1492</v>
+      </c>
+      <c r="G1234" s="9"/>
+      <c r="H1234" s="17"/>
+      <c r="I1234" s="29" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J1234" s="9"/>
+      <c r="K1234" s="9"/>
+      <c r="L1234" s="9"/>
+      <c r="M1234" s="17"/>
+    </row>
+    <row r="1235" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1235" s="12">
+        <v>5</v>
+      </c>
+      <c r="D1235" s="18" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E1235" s="20"/>
+      <c r="F1235" s="18" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1235" s="19"/>
+      <c r="H1235" s="20"/>
+      <c r="I1235" s="18" t="s">
+        <v>1496</v>
+      </c>
+      <c r="J1235" s="19"/>
+      <c r="K1235" s="19"/>
+      <c r="L1235" s="19"/>
+      <c r="M1235" s="20"/>
+    </row>
+    <row r="1238" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1238" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="1239" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1239" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="1240" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1240" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="1242" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1242" s="3" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="1243" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1243">
+        <v>1</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1244" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1244">
+        <v>2</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="1245" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1245">
+        <v>3</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="1246" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D1246" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1247" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1247">
+        <v>4</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C1249" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1252" s="3" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1254" s="3" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1255" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C1256" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C1257" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C1258" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C1259" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1261" s="3" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C1262" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C1263" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C1264" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="1266" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B1266" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1267" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C1267" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="1269" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C1269" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="1271" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B1271" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1272" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C1272" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1273" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D1273" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1275" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B1275" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1276" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C1276" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="1277" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C1277" s="62" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1278" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C1278" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="1279" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C1279" s="62" t="s">
+        <v>1527</v>
+      </c>
+      <c r="J1279" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="1281" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1281" s="62" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1282" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1282" s="62" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1283" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1283" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1285" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B1285" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="1287" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1287" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="1288" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1288" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1289" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1289" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="1290" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1290" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1291" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1291" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="1292" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1292" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="1293" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1293" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="1294" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1294" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1296" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1296" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="1298" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B1298" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="1299" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1299" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="1300" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1300" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="1302" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1302" s="3" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1303" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1303" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1304" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1304" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1305" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1305" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1306" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1306" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1307" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1307" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="1308" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1308" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1309" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1309" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1310" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1310" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1311" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1311" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1312" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C1312" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1313" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C1313" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="1314" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C1314" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1315" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C1315" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1316" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C1316" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1317" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C1317" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1320" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1320" s="11" t="s">
         <v>1377</v>
       </c>
-      <c r="D1177" s="13" t="s">
-        <v>1483</v>
-      </c>
-      <c r="E1177" s="15"/>
-      <c r="F1177" s="13" t="s">
-        <v>1484</v>
-      </c>
-      <c r="G1177" s="14"/>
-      <c r="H1177" s="15"/>
-      <c r="I1177" s="13" t="s">
-        <v>1379</v>
-      </c>
-      <c r="J1177" s="14"/>
-      <c r="K1177" s="14"/>
-      <c r="L1177" s="14"/>
-      <c r="M1177" s="15"/>
-    </row>
-    <row r="1178" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C1178" s="54">
+      <c r="C1320" s="13" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D1320" s="14"/>
+      <c r="E1320" s="15"/>
+      <c r="F1320" s="13" t="s">
+        <v>579</v>
+      </c>
+      <c r="G1320" s="14"/>
+      <c r="H1320" s="14"/>
+      <c r="I1320" s="14"/>
+      <c r="J1320" s="14"/>
+      <c r="K1320" s="15"/>
+    </row>
+    <row r="1321" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1321" s="53">
         <v>1</v>
       </c>
-      <c r="D1178" s="16" t="s">
-        <v>1485</v>
-      </c>
-      <c r="E1178" s="17"/>
-      <c r="F1178" s="16" t="s">
-        <v>1486</v>
-      </c>
-      <c r="G1178" s="9"/>
-      <c r="H1178" s="17"/>
-      <c r="I1178" s="16" t="s">
-        <v>1487</v>
-      </c>
-      <c r="J1178" s="9"/>
-      <c r="K1178" s="9"/>
-      <c r="L1178" s="9"/>
-      <c r="M1178" s="17"/>
-    </row>
-    <row r="1179" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C1179" s="54">
+      <c r="C1321" s="16" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D1321" s="9"/>
+      <c r="E1321" s="17"/>
+      <c r="F1321" s="16" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G1321" s="9"/>
+      <c r="H1321" s="9"/>
+      <c r="I1321" s="9"/>
+      <c r="J1321" s="9"/>
+      <c r="K1321" s="17"/>
+    </row>
+    <row r="1322" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1322" s="53">
         <v>2</v>
       </c>
-      <c r="D1179" s="16" t="s">
-        <v>1488</v>
-      </c>
-      <c r="E1179" s="17"/>
-      <c r="F1179" s="16" t="s">
-        <v>1486</v>
-      </c>
-      <c r="G1179" s="9"/>
-      <c r="H1179" s="17"/>
-      <c r="I1179" s="16" t="s">
-        <v>1489</v>
-      </c>
-      <c r="J1179" s="9"/>
-      <c r="K1179" s="9"/>
-      <c r="L1179" s="9"/>
-      <c r="M1179" s="17"/>
-    </row>
-    <row r="1180" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C1180" s="54">
+      <c r="C1322" s="16" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D1322" s="9"/>
+      <c r="E1322" s="17"/>
+      <c r="F1322" s="16" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G1322" s="9"/>
+      <c r="H1322" s="9"/>
+      <c r="I1322" s="9"/>
+      <c r="J1322" s="9"/>
+      <c r="K1322" s="17"/>
+    </row>
+    <row r="1323" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1323" s="53">
         <v>3</v>
       </c>
-      <c r="D1180" s="16" t="s">
-        <v>1490</v>
-      </c>
-      <c r="E1180" s="17"/>
-      <c r="F1180" s="29" t="s">
-        <v>1491</v>
-      </c>
-      <c r="G1180" s="9"/>
-      <c r="H1180" s="17"/>
-      <c r="I1180" s="29" t="s">
-        <v>1492</v>
-      </c>
-      <c r="J1180" s="9"/>
-      <c r="K1180" s="9"/>
-      <c r="L1180" s="9"/>
-      <c r="M1180" s="17"/>
-    </row>
-    <row r="1181" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C1181" s="54">
+      <c r="C1323" s="16" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D1323" s="9"/>
+      <c r="E1323" s="17"/>
+      <c r="F1323" s="16" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G1323" s="9"/>
+      <c r="H1323" s="9"/>
+      <c r="I1323" s="9"/>
+      <c r="J1323" s="9"/>
+      <c r="K1323" s="17"/>
+    </row>
+    <row r="1324" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1324" s="12">
         <v>4</v>
       </c>
-      <c r="D1181" s="16" t="s">
-        <v>1493</v>
-      </c>
-      <c r="E1181" s="17"/>
-      <c r="F1181" s="16" t="s">
-        <v>1494</v>
-      </c>
-      <c r="G1181" s="9"/>
-      <c r="H1181" s="17"/>
-      <c r="I1181" s="29" t="s">
-        <v>1495</v>
-      </c>
-      <c r="J1181" s="9"/>
-      <c r="K1181" s="9"/>
-      <c r="L1181" s="9"/>
-      <c r="M1181" s="17"/>
-    </row>
-    <row r="1182" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C1182" s="12">
-        <v>5</v>
-      </c>
-      <c r="D1182" s="18" t="s">
-        <v>1496</v>
-      </c>
-      <c r="E1182" s="20"/>
-      <c r="F1182" s="18" t="s">
-        <v>1497</v>
-      </c>
-      <c r="G1182" s="19"/>
-      <c r="H1182" s="20"/>
-      <c r="I1182" s="18" t="s">
-        <v>1498</v>
-      </c>
-      <c r="J1182" s="19"/>
-      <c r="K1182" s="19"/>
-      <c r="L1182" s="19"/>
-      <c r="M1182" s="20"/>
-    </row>
-    <row r="1185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1185" t="s">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="1186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C1186" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="1187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C1187" t="s">
-        <v>1502</v>
-      </c>
-    </row>
-    <row r="1189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1189" s="3" t="s">
-        <v>1589</v>
-      </c>
-    </row>
-    <row r="1190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1190">
-        <v>1</v>
-      </c>
-      <c r="C1190" t="s">
-        <v>1584</v>
-      </c>
-    </row>
-    <row r="1191" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1191">
-        <v>2</v>
-      </c>
-      <c r="C1191" t="s">
-        <v>1585</v>
-      </c>
-    </row>
-    <row r="1192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1192">
-        <v>3</v>
-      </c>
-      <c r="C1192" t="s">
-        <v>1587</v>
-      </c>
-    </row>
-    <row r="1193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D1193" t="s">
-        <v>1586</v>
-      </c>
-    </row>
-    <row r="1194" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1194">
-        <v>4</v>
-      </c>
-      <c r="C1194" t="s">
-        <v>1588</v>
-      </c>
-    </row>
-    <row r="1196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C1196" t="s">
+      <c r="C1324" s="18" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D1324" s="19"/>
+      <c r="E1324" s="20"/>
+      <c r="F1324" s="18" t="s">
+        <v>1547</v>
+      </c>
+      <c r="G1324" s="19"/>
+      <c r="H1324" s="19"/>
+      <c r="I1324" s="19"/>
+      <c r="J1324" s="19"/>
+      <c r="K1324" s="20"/>
+    </row>
+    <row r="1326" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1326" s="3" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="1327" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1327" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="1328" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1328" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1331" s="76" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1333" t="s">
+        <v>1882</v>
+      </c>
+      <c r="G1333" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1334" t="s">
+        <v>1883</v>
+      </c>
+      <c r="G1334" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1335" t="s">
+        <v>1884</v>
+      </c>
+      <c r="G1335" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1336" t="s">
+        <v>1885</v>
+      </c>
+      <c r="G1336" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1339" s="76" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1340" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C1341" t="s">
         <v>1590</v>
       </c>
     </row>
-    <row r="1199" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1199" s="3" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="1201" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B1201" s="3" t="s">
-        <v>1504</v>
-      </c>
-    </row>
-    <row r="1202" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B1202" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="1203" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1203" t="s">
-        <v>1506</v>
-      </c>
-    </row>
-    <row r="1204" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1204" t="s">
-        <v>1507</v>
-      </c>
-    </row>
-    <row r="1205" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1205" t="s">
-        <v>1508</v>
-      </c>
-    </row>
-    <row r="1206" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1206" t="s">
-        <v>1509</v>
-      </c>
-    </row>
-    <row r="1208" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B1208" s="3" t="s">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="1209" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1209" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="1210" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1210" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="1211" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1211" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="1213" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B1213" t="s">
-        <v>1511</v>
-      </c>
-    </row>
-    <row r="1214" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1214" t="s">
-        <v>1512</v>
-      </c>
-    </row>
-    <row r="1216" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1216" t="s">
-        <v>1513</v>
-      </c>
-    </row>
-    <row r="1218" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B1218" t="s">
-        <v>1514</v>
-      </c>
-    </row>
-    <row r="1219" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1219" t="s">
-        <v>1515</v>
-      </c>
-    </row>
-    <row r="1220" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D1220" t="s">
-        <v>1516</v>
-      </c>
-    </row>
-    <row r="1222" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B1222" t="s">
-        <v>1517</v>
-      </c>
-    </row>
-    <row r="1223" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1223" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="1224" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1224" s="63" t="s">
-        <v>1521</v>
-      </c>
-    </row>
-    <row r="1225" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1225" t="s">
-        <v>1522</v>
-      </c>
-    </row>
-    <row r="1226" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1226" s="63" t="s">
-        <v>1529</v>
-      </c>
-      <c r="J1226" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="1228" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1228" s="63" t="s">
-        <v>1518</v>
-      </c>
-    </row>
-    <row r="1229" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1229" s="63" t="s">
-        <v>1519</v>
-      </c>
-    </row>
-    <row r="1230" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1230" t="s">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="1232" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B1232" t="s">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="1234" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1234" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="1235" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1235" t="s">
-        <v>1524</v>
-      </c>
-    </row>
-    <row r="1236" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1236" t="s">
-        <v>1531</v>
-      </c>
-    </row>
-    <row r="1237" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1237" t="s">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="1238" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1238" t="s">
-        <v>1526</v>
-      </c>
-    </row>
-    <row r="1239" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1239" t="s">
-        <v>1527</v>
-      </c>
-    </row>
-    <row r="1240" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1240" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="1241" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1241" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="1243" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1243" t="s">
-        <v>1532</v>
-      </c>
-    </row>
-    <row r="1245" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B1245" t="s">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="1246" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1246" t="s">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="1247" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C1247" t="s">
-        <v>1535</v>
-      </c>
-    </row>
-    <row r="1249" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1249" s="3" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="1250" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1250" t="s">
-        <v>1494</v>
-      </c>
-    </row>
-    <row r="1251" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1251" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="1252" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1252" t="s">
-        <v>1506</v>
-      </c>
-    </row>
-    <row r="1253" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1253" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="1254" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1254" t="s">
-        <v>1536</v>
-      </c>
-    </row>
-    <row r="1255" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1255" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="1256" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1256" t="s">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="1257" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1257" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="1258" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1258" t="s">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="1259" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1259" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="1260" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1260" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="1261" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1261" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="1262" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1262" t="s">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="1263" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1263" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="1264" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C1264" t="s">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="1267" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1267" s="11" t="s">
-        <v>1377</v>
-      </c>
-      <c r="C1267" s="13" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D1267" s="14"/>
-      <c r="E1267" s="15"/>
-      <c r="F1267" s="13" t="s">
-        <v>579</v>
-      </c>
-      <c r="G1267" s="14"/>
-      <c r="H1267" s="14"/>
-      <c r="I1267" s="14"/>
-      <c r="J1267" s="14"/>
-      <c r="K1267" s="15"/>
-    </row>
-    <row r="1268" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1268" s="54">
-        <v>1</v>
-      </c>
-      <c r="C1268" s="16" t="s">
-        <v>1506</v>
-      </c>
-      <c r="D1268" s="9"/>
-      <c r="E1268" s="17"/>
-      <c r="F1268" s="16" t="s">
-        <v>1545</v>
-      </c>
-      <c r="G1268" s="9"/>
-      <c r="H1268" s="9"/>
-      <c r="I1268" s="9"/>
-      <c r="J1268" s="9"/>
-      <c r="K1268" s="17"/>
-    </row>
-    <row r="1269" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1269" s="54">
-        <v>2</v>
-      </c>
-      <c r="C1269" s="16" t="s">
-        <v>1546</v>
-      </c>
-      <c r="D1269" s="9"/>
-      <c r="E1269" s="17"/>
-      <c r="F1269" s="16" t="s">
-        <v>1547</v>
-      </c>
-      <c r="G1269" s="9"/>
-      <c r="H1269" s="9"/>
-      <c r="I1269" s="9"/>
-      <c r="J1269" s="9"/>
-      <c r="K1269" s="17"/>
-    </row>
-    <row r="1270" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1270" s="54">
-        <v>3</v>
-      </c>
-      <c r="C1270" s="16" t="s">
-        <v>1539</v>
-      </c>
-      <c r="D1270" s="9"/>
-      <c r="E1270" s="17"/>
-      <c r="F1270" s="16" t="s">
-        <v>1548</v>
-      </c>
-      <c r="G1270" s="9"/>
-      <c r="H1270" s="9"/>
-      <c r="I1270" s="9"/>
-      <c r="J1270" s="9"/>
-      <c r="K1270" s="17"/>
-    </row>
-    <row r="1271" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1271" s="12">
-        <v>4</v>
-      </c>
-      <c r="C1271" s="18" t="s">
-        <v>1540</v>
-      </c>
-      <c r="D1271" s="19"/>
-      <c r="E1271" s="20"/>
-      <c r="F1271" s="18" t="s">
-        <v>1549</v>
-      </c>
-      <c r="G1271" s="19"/>
-      <c r="H1271" s="19"/>
-      <c r="I1271" s="19"/>
-      <c r="J1271" s="19"/>
-      <c r="K1271" s="20"/>
-    </row>
-    <row r="1273" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1273" s="3" t="s">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="1274" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1274" t="s">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="1275" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1275" t="s">
-        <v>1552</v>
-      </c>
-    </row>
-    <row r="1278" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1278" s="78" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="1280" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1280" t="s">
-        <v>1884</v>
-      </c>
-      <c r="G1280" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="1281" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B1281" t="s">
-        <v>1885</v>
-      </c>
-      <c r="G1281" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="1282" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B1282" t="s">
-        <v>1886</v>
-      </c>
-      <c r="G1282" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="1283" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B1283" t="s">
-        <v>1887</v>
-      </c>
-      <c r="G1283" t="s">
-        <v>1887</v>
-      </c>
+    <row r="1342" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1342" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C1343" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="1345" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B1345" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1346" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C1346" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="1347" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C1347" s="2" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="1348" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B1348" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="1349" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C1349" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="1350" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D1350" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="1352" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C1352" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="1353" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D1353" t="s">
+        <v>1936</v>
+      </c>
+      <c r="H1353" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="1354" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D1354" t="s">
+        <v>1937</v>
+      </c>
+      <c r="I1354" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="1355" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I1355" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1356" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B1356" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="1357" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C1357" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="1358" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C1358" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="1359" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C1359" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="1360" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C1360" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1361" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1362" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D1363" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D1364" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D1366" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E1367" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1369" s="76" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1370" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1371" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1372" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1373" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1374" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1375" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D1376" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="1377" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="E1377" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1378" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="E1378" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="1379" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="E1379" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="1380" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="E1380" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1381" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D1381" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="1382" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D1382" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="1384" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1384" s="76" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="1385" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1385" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="1386" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C1386" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="1388" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1388" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1388" s="14"/>
+      <c r="D1388" s="14"/>
+      <c r="E1388" s="14"/>
+      <c r="F1388" s="14"/>
+      <c r="G1388" s="15"/>
+      <c r="H1388" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="I1388" s="14"/>
+      <c r="J1388" s="14"/>
+      <c r="K1388" s="14"/>
+      <c r="L1388" s="14"/>
+      <c r="M1388" s="15"/>
+    </row>
+    <row r="1389" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1389" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="C1389" s="9"/>
+      <c r="D1389" s="9"/>
+      <c r="E1389" s="9"/>
+      <c r="F1389" s="9"/>
+      <c r="G1389" s="17"/>
+      <c r="H1389" s="16" t="s">
+        <v>1965</v>
+      </c>
+      <c r="I1389" s="9"/>
+      <c r="J1389" s="9"/>
+      <c r="K1389" s="9"/>
+      <c r="L1389" s="9"/>
+      <c r="M1389" s="17"/>
+    </row>
+    <row r="1390" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1390" s="16" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C1390" s="9"/>
+      <c r="D1390" s="9"/>
+      <c r="E1390" s="9"/>
+      <c r="F1390" s="9"/>
+      <c r="G1390" s="17"/>
+      <c r="H1390" s="16"/>
+      <c r="I1390" s="9"/>
+      <c r="J1390" s="9"/>
+      <c r="K1390" s="9"/>
+      <c r="L1390" s="9"/>
+      <c r="M1390" s="17"/>
+    </row>
+    <row r="1391" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1391" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="C1391" s="9"/>
+      <c r="D1391" s="9"/>
+      <c r="E1391" s="9"/>
+      <c r="F1391" s="9"/>
+      <c r="G1391" s="17"/>
+      <c r="H1391" s="16" t="s">
+        <v>1881</v>
+      </c>
+      <c r="I1391" s="9"/>
+      <c r="J1391" s="9"/>
+      <c r="K1391" s="9"/>
+      <c r="L1391" s="9"/>
+      <c r="M1391" s="17"/>
+    </row>
+    <row r="1392" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1392" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="C1392" s="9"/>
+      <c r="D1392" s="9"/>
+      <c r="E1392" s="9"/>
+      <c r="F1392" s="9"/>
+      <c r="G1392" s="17"/>
+      <c r="H1392" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1392" s="9"/>
+      <c r="J1392" s="9"/>
+      <c r="K1392" s="9"/>
+      <c r="L1392" s="9"/>
+      <c r="M1392" s="17"/>
+    </row>
+    <row r="1393" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1393" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="C1393" s="9"/>
+      <c r="D1393" s="9"/>
+      <c r="E1393" s="9"/>
+      <c r="F1393" s="9"/>
+      <c r="G1393" s="17"/>
+      <c r="H1393" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I1393" s="9"/>
+      <c r="J1393" s="9"/>
+      <c r="K1393" s="9"/>
+      <c r="L1393" s="9"/>
+      <c r="M1393" s="17"/>
+    </row>
+    <row r="1394" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1394" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="C1394" s="9"/>
+      <c r="D1394" s="9"/>
+      <c r="E1394" s="9"/>
+      <c r="F1394" s="9"/>
+      <c r="G1394" s="17"/>
+      <c r="H1394" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1394" s="9"/>
+      <c r="J1394" s="9"/>
+      <c r="K1394" s="9"/>
+      <c r="L1394" s="9"/>
+      <c r="M1394" s="17"/>
+    </row>
+    <row r="1395" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1395" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="C1395" s="9"/>
+      <c r="D1395" s="9"/>
+      <c r="E1395" s="9"/>
+      <c r="F1395" s="9"/>
+      <c r="G1395" s="17"/>
+      <c r="H1395" s="16"/>
+      <c r="I1395" s="9"/>
+      <c r="J1395" s="9"/>
+      <c r="K1395" s="9"/>
+      <c r="L1395" s="9"/>
+      <c r="M1395" s="17"/>
+    </row>
+    <row r="1396" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1396" s="16" t="s">
+        <v>834</v>
+      </c>
+      <c r="C1396" s="9"/>
+      <c r="D1396" s="9"/>
+      <c r="E1396" s="9"/>
+      <c r="F1396" s="9"/>
+      <c r="G1396" s="17"/>
+      <c r="H1396" s="16" t="s">
+        <v>1973</v>
+      </c>
+      <c r="I1396" s="9"/>
+      <c r="J1396" s="9"/>
+      <c r="K1396" s="9"/>
+      <c r="L1396" s="9"/>
+      <c r="M1396" s="17"/>
+    </row>
+    <row r="1397" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1397" s="16"/>
+      <c r="C1397" s="9"/>
+      <c r="D1397" s="9"/>
+      <c r="E1397" s="9"/>
+      <c r="F1397" s="9"/>
+      <c r="G1397" s="17"/>
+      <c r="H1397" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1397" s="9"/>
+      <c r="J1397" s="9"/>
+      <c r="K1397" s="9"/>
+      <c r="L1397" s="9"/>
+      <c r="M1397" s="17"/>
+    </row>
+    <row r="1398" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1398" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="C1398" s="9"/>
+      <c r="D1398" s="9"/>
+      <c r="E1398" s="9"/>
+      <c r="F1398" s="9"/>
+      <c r="G1398" s="17"/>
+      <c r="H1398" s="16" t="s">
+        <v>1972</v>
+      </c>
+      <c r="I1398" s="9"/>
+      <c r="J1398" s="9"/>
+      <c r="K1398" s="9"/>
+      <c r="L1398" s="9"/>
+      <c r="M1398" s="17"/>
+    </row>
+    <row r="1399" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1399" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1399" s="9"/>
+      <c r="D1399" s="9"/>
+      <c r="E1399" s="9"/>
+      <c r="F1399" s="9"/>
+      <c r="G1399" s="17"/>
+      <c r="H1399" s="16"/>
+      <c r="I1399" s="9"/>
+      <c r="J1399" s="9"/>
+      <c r="K1399" s="9"/>
+      <c r="L1399" s="9"/>
+      <c r="M1399" s="17"/>
+    </row>
+    <row r="1400" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1400" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="C1400" s="19"/>
+      <c r="D1400" s="19"/>
+      <c r="E1400" s="19"/>
+      <c r="F1400" s="19"/>
+      <c r="G1400" s="20"/>
+      <c r="H1400" s="18"/>
+      <c r="I1400" s="19"/>
+      <c r="J1400" s="19"/>
+      <c r="K1400" s="19"/>
+      <c r="L1400" s="19"/>
+      <c r="M1400" s="20"/>
+    </row>
+    <row r="1403" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1403" s="26" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C1403" s="14"/>
+      <c r="D1403" s="14"/>
+      <c r="E1403" s="14"/>
+      <c r="F1403" s="14"/>
+      <c r="G1403" s="15"/>
+      <c r="H1403" s="26" t="s">
+        <v>1951</v>
+      </c>
+      <c r="I1403" s="14"/>
+      <c r="J1403" s="14"/>
+      <c r="K1403" s="14"/>
+      <c r="L1403" s="14"/>
+      <c r="M1403" s="15"/>
+    </row>
+    <row r="1404" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1404" s="16" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C1404" s="9"/>
+      <c r="D1404" s="9"/>
+      <c r="E1404" s="9"/>
+      <c r="F1404" s="9"/>
+      <c r="G1404" s="17"/>
+      <c r="H1404" s="18" t="s">
+        <v>1968</v>
+      </c>
+      <c r="I1404" s="19"/>
+      <c r="J1404" s="19"/>
+      <c r="K1404" s="19"/>
+      <c r="L1404" s="19"/>
+      <c r="M1404" s="20"/>
+    </row>
+    <row r="1405" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1405" s="16" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C1405" s="9"/>
+      <c r="D1405" s="9"/>
+      <c r="E1405" s="9"/>
+      <c r="F1405" s="9"/>
+      <c r="G1405" s="17"/>
+    </row>
+    <row r="1406" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1406" s="16" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C1406" s="9"/>
+      <c r="D1406" s="9"/>
+      <c r="E1406" s="9"/>
+      <c r="F1406" s="9"/>
+      <c r="G1406" s="17"/>
+    </row>
+    <row r="1407" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1407" s="16" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C1407" s="9"/>
+      <c r="D1407" s="9"/>
+      <c r="E1407" s="9"/>
+      <c r="F1407" s="9"/>
+      <c r="G1407" s="17"/>
+    </row>
+    <row r="1408" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B1408" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="C1408" s="9"/>
+      <c r="D1408" s="9"/>
+      <c r="E1408" s="9"/>
+      <c r="F1408" s="9"/>
+      <c r="G1408" s="17"/>
+    </row>
+    <row r="1409" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1409" s="16"/>
+      <c r="C1409" s="9"/>
+      <c r="D1409" s="9"/>
+      <c r="E1409" s="9"/>
+      <c r="F1409" s="9"/>
+      <c r="G1409" s="17"/>
+    </row>
+    <row r="1410" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1410" s="16" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C1410" s="9"/>
+      <c r="D1410" s="9"/>
+      <c r="E1410" s="9"/>
+      <c r="F1410" s="9"/>
+      <c r="G1410" s="17"/>
+    </row>
+    <row r="1411" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1411" s="16" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C1411" s="9"/>
+      <c r="D1411" s="9"/>
+      <c r="E1411" s="9"/>
+      <c r="F1411" s="9"/>
+      <c r="G1411" s="17"/>
+    </row>
+    <row r="1412" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1412" s="16"/>
+      <c r="C1412" s="9"/>
+      <c r="D1412" s="9"/>
+      <c r="E1412" s="9"/>
+      <c r="F1412" s="9"/>
+      <c r="G1412" s="17"/>
+    </row>
+    <row r="1413" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1413" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1413" s="9"/>
+      <c r="D1413" s="9"/>
+      <c r="E1413" s="9"/>
+      <c r="F1413" s="9"/>
+      <c r="G1413" s="17"/>
+    </row>
+    <row r="1414" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1414" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="C1414" s="9"/>
+      <c r="D1414" s="9"/>
+      <c r="E1414" s="9"/>
+      <c r="F1414" s="9"/>
+      <c r="G1414" s="17"/>
+    </row>
+    <row r="1415" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1415" s="16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C1415" s="9"/>
+      <c r="D1415" s="9"/>
+      <c r="E1415" s="9"/>
+      <c r="F1415" s="9"/>
+      <c r="G1415" s="17"/>
+    </row>
+    <row r="1416" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1416" s="16" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1416" s="9"/>
+      <c r="D1416" s="9"/>
+      <c r="E1416" s="9"/>
+      <c r="F1416" s="9"/>
+      <c r="G1416" s="17"/>
+    </row>
+    <row r="1417" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1417" s="16"/>
+      <c r="C1417" s="9"/>
+      <c r="D1417" s="9"/>
+      <c r="E1417" s="9"/>
+      <c r="F1417" s="9"/>
+      <c r="G1417" s="17"/>
+    </row>
+    <row r="1418" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1418" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="C1418" s="9"/>
+      <c r="D1418" s="9"/>
+      <c r="E1418" s="9"/>
+      <c r="F1418" s="9"/>
+      <c r="G1418" s="17"/>
+    </row>
+    <row r="1419" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1419" s="16" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C1419" s="9"/>
+      <c r="D1419" s="9"/>
+      <c r="E1419" s="9"/>
+      <c r="F1419" s="9"/>
+      <c r="G1419" s="17"/>
+    </row>
+    <row r="1420" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1420" s="18" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C1420" s="19"/>
+      <c r="D1420" s="19"/>
+      <c r="E1420" s="19"/>
+      <c r="F1420" s="19"/>
+      <c r="G1420" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/examsDjangoBasics.xlsx
+++ b/examsDjangoBasics.xlsx
@@ -37113,12 +37113,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="65">
+  <fonts count="66">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -37864,19 +37872,19 @@
   </cellStyleXfs>
   <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -37891,63 +37899,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
